--- a/VerveStacks_ESP_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ESP_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ESP_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FB4B3EB-7EC4-42AF-B847-0178B614A389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBBB4B14-CBD5-46B1-9F4E-FE553EC81220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2792" uniqueCount="1440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="794">
   <si>
     <t>~TFM_Psets</t>
   </si>
@@ -2008,2356 +2008,418 @@
     <t>e_ES6*</t>
   </si>
   <si>
-    <t>rez_ESP_0</t>
-  </si>
-  <si>
-    <t>elc*ESP_0000</t>
-  </si>
-  <si>
-    <t>rez_ESP_1</t>
-  </si>
-  <si>
-    <t>elc*ESP_0001</t>
-  </si>
-  <si>
-    <t>rez_ESP_2</t>
-  </si>
-  <si>
-    <t>elc*ESP_0002</t>
-  </si>
-  <si>
-    <t>rez_ESP_3</t>
-  </si>
-  <si>
-    <t>elc*ESP_0003</t>
-  </si>
-  <si>
-    <t>rez_ESP_4</t>
-  </si>
-  <si>
-    <t>elc*ESP_0004</t>
-  </si>
-  <si>
-    <t>rez_ESP_5</t>
-  </si>
-  <si>
-    <t>elc*ESP_0005</t>
-  </si>
-  <si>
-    <t>rez_ESP_6</t>
-  </si>
-  <si>
-    <t>elc*ESP_0006</t>
-  </si>
-  <si>
-    <t>rez_ESP_7</t>
-  </si>
-  <si>
-    <t>elc*ESP_0007</t>
-  </si>
-  <si>
-    <t>rez_ESP_8</t>
-  </si>
-  <si>
-    <t>elc*ESP_0008</t>
-  </si>
-  <si>
-    <t>rez_ESP_9</t>
-  </si>
-  <si>
-    <t>elc*ESP_0009</t>
-  </si>
-  <si>
-    <t>rez_ESP_10</t>
-  </si>
-  <si>
-    <t>elc*ESP_0010</t>
-  </si>
-  <si>
-    <t>rez_ESP_11</t>
-  </si>
-  <si>
-    <t>elc*ESP_0011</t>
-  </si>
-  <si>
-    <t>rez_ESP_12</t>
-  </si>
-  <si>
-    <t>elc*ESP_0012</t>
-  </si>
-  <si>
-    <t>rez_ESP_13</t>
-  </si>
-  <si>
-    <t>elc*ESP_0013</t>
-  </si>
-  <si>
-    <t>rez_ESP_14</t>
-  </si>
-  <si>
-    <t>elc*ESP_0014</t>
-  </si>
-  <si>
-    <t>rez_ESP_15</t>
-  </si>
-  <si>
-    <t>elc*ESP_0015</t>
-  </si>
-  <si>
-    <t>rez_ESP_16</t>
-  </si>
-  <si>
-    <t>elc*ESP_0016</t>
-  </si>
-  <si>
-    <t>rez_ESP_17</t>
-  </si>
-  <si>
-    <t>elc*ESP_0017</t>
-  </si>
-  <si>
-    <t>rez_ESP_18</t>
-  </si>
-  <si>
-    <t>elc*ESP_0018</t>
-  </si>
-  <si>
-    <t>rez_ESP_19</t>
-  </si>
-  <si>
-    <t>elc*ESP_0019</t>
-  </si>
-  <si>
-    <t>rez_ESP_20</t>
-  </si>
-  <si>
-    <t>elc*ESP_0020</t>
-  </si>
-  <si>
-    <t>rez_ESP_21</t>
-  </si>
-  <si>
-    <t>elc*ESP_0021</t>
-  </si>
-  <si>
-    <t>rez_ESP_22</t>
-  </si>
-  <si>
-    <t>elc*ESP_0022</t>
-  </si>
-  <si>
-    <t>rez_ESP_23</t>
-  </si>
-  <si>
-    <t>elc*ESP_0023</t>
-  </si>
-  <si>
-    <t>rez_ESP_24</t>
-  </si>
-  <si>
-    <t>elc*ESP_0024</t>
-  </si>
-  <si>
-    <t>rez_ESP_25</t>
-  </si>
-  <si>
-    <t>elc*ESP_0025</t>
-  </si>
-  <si>
-    <t>rez_ESP_26</t>
-  </si>
-  <si>
-    <t>elc*ESP_0026</t>
-  </si>
-  <si>
-    <t>rez_ESP_27</t>
-  </si>
-  <si>
-    <t>elc*ESP_0027</t>
-  </si>
-  <si>
-    <t>rez_ESP_28</t>
-  </si>
-  <si>
-    <t>elc*ESP_0028</t>
-  </si>
-  <si>
-    <t>rez_ESP_29</t>
-  </si>
-  <si>
-    <t>elc*ESP_0029</t>
-  </si>
-  <si>
-    <t>rez_ESP_30</t>
-  </si>
-  <si>
-    <t>elc*ESP_0030</t>
-  </si>
-  <si>
-    <t>rez_ESP_31</t>
-  </si>
-  <si>
-    <t>elc*ESP_0031</t>
-  </si>
-  <si>
-    <t>rez_ESP_32</t>
-  </si>
-  <si>
-    <t>elc*ESP_0032</t>
-  </si>
-  <si>
-    <t>rez_ESP_33</t>
-  </si>
-  <si>
-    <t>elc*ESP_0033</t>
-  </si>
-  <si>
-    <t>rez_ESP_34</t>
-  </si>
-  <si>
-    <t>elc*ESP_0034</t>
-  </si>
-  <si>
-    <t>rez_ESP_35</t>
-  </si>
-  <si>
-    <t>elc*ESP_0035</t>
-  </si>
-  <si>
-    <t>rez_ESP_36</t>
-  </si>
-  <si>
-    <t>elc*ESP_0036</t>
-  </si>
-  <si>
-    <t>rez_ESP_37</t>
-  </si>
-  <si>
-    <t>elc*ESP_0037</t>
-  </si>
-  <si>
-    <t>rez_ESP_38</t>
-  </si>
-  <si>
-    <t>elc*ESP_0038</t>
-  </si>
-  <si>
-    <t>rez_ESP_39</t>
-  </si>
-  <si>
-    <t>elc*ESP_0039</t>
-  </si>
-  <si>
-    <t>rez_ESP_40</t>
-  </si>
-  <si>
-    <t>elc*ESP_0040</t>
-  </si>
-  <si>
-    <t>rez_ESP_41</t>
-  </si>
-  <si>
-    <t>elc*ESP_0041</t>
-  </si>
-  <si>
-    <t>rez_ESP_42</t>
-  </si>
-  <si>
-    <t>elc*ESP_0042</t>
-  </si>
-  <si>
-    <t>rez_ESP_43</t>
-  </si>
-  <si>
-    <t>elc*ESP_0043</t>
-  </si>
-  <si>
-    <t>rez_ESP_44</t>
-  </si>
-  <si>
-    <t>elc*ESP_0044</t>
-  </si>
-  <si>
-    <t>rez_ESP_45</t>
-  </si>
-  <si>
-    <t>elc*ESP_0045</t>
-  </si>
-  <si>
-    <t>rez_ESP_46</t>
-  </si>
-  <si>
-    <t>elc*ESP_0046</t>
-  </si>
-  <si>
-    <t>rez_ESP_47</t>
-  </si>
-  <si>
-    <t>elc*ESP_0047</t>
-  </si>
-  <si>
-    <t>rez_ESP_48</t>
-  </si>
-  <si>
-    <t>elc*ESP_0048</t>
-  </si>
-  <si>
-    <t>rez_ESP_49</t>
-  </si>
-  <si>
-    <t>elc*ESP_0049</t>
-  </si>
-  <si>
-    <t>rez_ESP_50</t>
-  </si>
-  <si>
-    <t>elc*ESP_0050</t>
-  </si>
-  <si>
-    <t>rez_ESP_51</t>
-  </si>
-  <si>
-    <t>elc*ESP_0051</t>
-  </si>
-  <si>
-    <t>rez_ESP_52</t>
-  </si>
-  <si>
-    <t>elc*ESP_0052</t>
-  </si>
-  <si>
-    <t>rez_ESP_53</t>
-  </si>
-  <si>
-    <t>elc*ESP_0053</t>
-  </si>
-  <si>
-    <t>rez_ESP_54</t>
-  </si>
-  <si>
-    <t>elc*ESP_0054</t>
-  </si>
-  <si>
-    <t>rez_ESP_55</t>
-  </si>
-  <si>
-    <t>elc*ESP_0055</t>
-  </si>
-  <si>
-    <t>rez_ESP_56</t>
-  </si>
-  <si>
-    <t>elc*ESP_0056</t>
-  </si>
-  <si>
-    <t>rez_ESP_57</t>
-  </si>
-  <si>
-    <t>elc*ESP_0057</t>
-  </si>
-  <si>
-    <t>rez_ESP_58</t>
-  </si>
-  <si>
-    <t>elc*ESP_0058</t>
-  </si>
-  <si>
-    <t>rez_ESP_59</t>
-  </si>
-  <si>
-    <t>elc*ESP_0059</t>
-  </si>
-  <si>
-    <t>rez_ESP_60</t>
-  </si>
-  <si>
-    <t>elc*ESP_0060</t>
-  </si>
-  <si>
-    <t>rez_ESP_61</t>
-  </si>
-  <si>
-    <t>elc*ESP_0061</t>
-  </si>
-  <si>
-    <t>rez_ESP_62</t>
-  </si>
-  <si>
-    <t>elc*ESP_0062</t>
-  </si>
-  <si>
-    <t>rez_ESP_63</t>
-  </si>
-  <si>
-    <t>elc*ESP_0063</t>
-  </si>
-  <si>
-    <t>rez_ESP_64</t>
-  </si>
-  <si>
-    <t>elc*ESP_0064</t>
-  </si>
-  <si>
-    <t>rez_ESP_65</t>
-  </si>
-  <si>
-    <t>elc*ESP_0065</t>
-  </si>
-  <si>
-    <t>rez_ESP_66</t>
-  </si>
-  <si>
-    <t>elc*ESP_0066</t>
-  </si>
-  <si>
-    <t>rez_ESP_67</t>
-  </si>
-  <si>
-    <t>elc*ESP_0067</t>
-  </si>
-  <si>
-    <t>rez_ESP_68</t>
-  </si>
-  <si>
-    <t>elc*ESP_0068</t>
-  </si>
-  <si>
-    <t>rez_ESP_69</t>
-  </si>
-  <si>
-    <t>elc*ESP_0069</t>
-  </si>
-  <si>
-    <t>rez_ESP_70</t>
-  </si>
-  <si>
-    <t>elc*ESP_0070</t>
-  </si>
-  <si>
-    <t>rez_ESP_71</t>
-  </si>
-  <si>
-    <t>elc*ESP_0071</t>
-  </si>
-  <si>
-    <t>rez_ESP_72</t>
-  </si>
-  <si>
-    <t>elc*ESP_0072</t>
-  </si>
-  <si>
-    <t>rez_ESP_73</t>
-  </si>
-  <si>
-    <t>elc*ESP_0073</t>
-  </si>
-  <si>
-    <t>rez_ESP_74</t>
-  </si>
-  <si>
-    <t>elc*ESP_0074</t>
-  </si>
-  <si>
-    <t>rez_ESP_75</t>
-  </si>
-  <si>
-    <t>elc*ESP_0075</t>
-  </si>
-  <si>
-    <t>rez_ESP_76</t>
-  </si>
-  <si>
-    <t>elc*ESP_0076</t>
-  </si>
-  <si>
-    <t>rez_ESP_77</t>
-  </si>
-  <si>
-    <t>elc*ESP_0077</t>
-  </si>
-  <si>
-    <t>rez_ESP_78</t>
-  </si>
-  <si>
-    <t>elc*ESP_0078</t>
-  </si>
-  <si>
-    <t>rez_ESP_79</t>
-  </si>
-  <si>
-    <t>elc*ESP_0079</t>
-  </si>
-  <si>
-    <t>rez_ESP_80</t>
-  </si>
-  <si>
-    <t>elc*ESP_0080</t>
-  </si>
-  <si>
-    <t>rez_ESP_81</t>
-  </si>
-  <si>
-    <t>elc*ESP_0081</t>
-  </si>
-  <si>
-    <t>rez_ESP_82</t>
-  </si>
-  <si>
-    <t>elc*ESP_0082</t>
-  </si>
-  <si>
-    <t>rez_ESP_83</t>
-  </si>
-  <si>
-    <t>elc*ESP_0083</t>
-  </si>
-  <si>
-    <t>rez_ESP_84</t>
-  </si>
-  <si>
-    <t>elc*ESP_0084</t>
-  </si>
-  <si>
-    <t>rez_ESP_85</t>
-  </si>
-  <si>
-    <t>elc*ESP_0085</t>
-  </si>
-  <si>
-    <t>rez_ESP_86</t>
-  </si>
-  <si>
-    <t>elc*ESP_0086</t>
-  </si>
-  <si>
-    <t>rez_ESP_87</t>
-  </si>
-  <si>
-    <t>elc*ESP_0087</t>
-  </si>
-  <si>
-    <t>rez_ESP_88</t>
-  </si>
-  <si>
-    <t>elc*ESP_0088</t>
-  </si>
-  <si>
-    <t>rez_ESP_89</t>
-  </si>
-  <si>
-    <t>elc*ESP_0089</t>
-  </si>
-  <si>
-    <t>rez_ESP_90</t>
-  </si>
-  <si>
-    <t>elc*ESP_0090</t>
-  </si>
-  <si>
-    <t>rez_ESP_91</t>
-  </si>
-  <si>
-    <t>elc*ESP_0091</t>
-  </si>
-  <si>
-    <t>rez_ESP_92</t>
-  </si>
-  <si>
-    <t>elc*ESP_0092</t>
-  </si>
-  <si>
-    <t>rez_ESP_93</t>
-  </si>
-  <si>
-    <t>elc*ESP_0093</t>
-  </si>
-  <si>
-    <t>rez_ESP_94</t>
-  </si>
-  <si>
-    <t>elc*ESP_0094</t>
-  </si>
-  <si>
-    <t>rez_ESP_95</t>
-  </si>
-  <si>
-    <t>elc*ESP_0095</t>
-  </si>
-  <si>
-    <t>rez_ESP_96</t>
-  </si>
-  <si>
-    <t>elc*ESP_0096</t>
-  </si>
-  <si>
-    <t>rez_ESP_97</t>
-  </si>
-  <si>
-    <t>elc*ESP_0097</t>
-  </si>
-  <si>
-    <t>rez_ESP_98</t>
-  </si>
-  <si>
-    <t>elc*ESP_0098</t>
-  </si>
-  <si>
-    <t>rez_ESP_99</t>
-  </si>
-  <si>
-    <t>elc*ESP_0099</t>
-  </si>
-  <si>
-    <t>rez_ESP_100</t>
-  </si>
-  <si>
-    <t>elc*ESP_0100</t>
-  </si>
-  <si>
-    <t>rez_ESP_101</t>
-  </si>
-  <si>
-    <t>elc*ESP_0101</t>
-  </si>
-  <si>
-    <t>rez_ESP_102</t>
-  </si>
-  <si>
-    <t>elc*ESP_0102</t>
-  </si>
-  <si>
-    <t>rez_ESP_103</t>
-  </si>
-  <si>
-    <t>elc*ESP_0103</t>
-  </si>
-  <si>
-    <t>rez_ESP_104</t>
-  </si>
-  <si>
-    <t>elc*ESP_0104</t>
-  </si>
-  <si>
-    <t>rez_ESP_105</t>
-  </si>
-  <si>
-    <t>elc*ESP_0105</t>
-  </si>
-  <si>
-    <t>rez_ESP_106</t>
-  </si>
-  <si>
-    <t>elc*ESP_0106</t>
-  </si>
-  <si>
-    <t>rez_ESP_107</t>
-  </si>
-  <si>
-    <t>elc*ESP_0107</t>
-  </si>
-  <si>
-    <t>rez_ESP_108</t>
-  </si>
-  <si>
-    <t>elc*ESP_0108</t>
-  </si>
-  <si>
-    <t>rez_ESP_109</t>
-  </si>
-  <si>
-    <t>elc*ESP_0109</t>
-  </si>
-  <si>
-    <t>rez_ESP_110</t>
-  </si>
-  <si>
-    <t>elc*ESP_0110</t>
-  </si>
-  <si>
-    <t>rez_ESP_111</t>
-  </si>
-  <si>
-    <t>elc*ESP_0111</t>
-  </si>
-  <si>
-    <t>rez_ESP_112</t>
-  </si>
-  <si>
-    <t>elc*ESP_0112</t>
-  </si>
-  <si>
-    <t>rez_ESP_113</t>
-  </si>
-  <si>
-    <t>elc*ESP_0113</t>
-  </si>
-  <si>
-    <t>rez_ESP_114</t>
-  </si>
-  <si>
-    <t>elc*ESP_0114</t>
-  </si>
-  <si>
-    <t>rez_ESP_115</t>
-  </si>
-  <si>
-    <t>elc*ESP_0115</t>
-  </si>
-  <si>
-    <t>rez_ESP_116</t>
-  </si>
-  <si>
-    <t>elc*ESP_0116</t>
-  </si>
-  <si>
-    <t>rez_ESP_117</t>
-  </si>
-  <si>
-    <t>elc*ESP_0117</t>
-  </si>
-  <si>
-    <t>rez_ESP_118</t>
-  </si>
-  <si>
-    <t>elc*ESP_0118</t>
-  </si>
-  <si>
-    <t>rez_ESP_119</t>
-  </si>
-  <si>
-    <t>elc*ESP_0119</t>
-  </si>
-  <si>
-    <t>rez_ESP_120</t>
-  </si>
-  <si>
-    <t>elc*ESP_0120</t>
-  </si>
-  <si>
-    <t>rez_ESP_121</t>
-  </si>
-  <si>
-    <t>elc*ESP_0121</t>
-  </si>
-  <si>
-    <t>rez_ESP_122</t>
-  </si>
-  <si>
-    <t>elc*ESP_0122</t>
-  </si>
-  <si>
-    <t>rez_ESP_123</t>
-  </si>
-  <si>
-    <t>elc*ESP_0123</t>
-  </si>
-  <si>
-    <t>rez_ESP_124</t>
-  </si>
-  <si>
-    <t>elc*ESP_0124</t>
-  </si>
-  <si>
-    <t>rez_ESP_125</t>
-  </si>
-  <si>
-    <t>elc*ESP_0125</t>
-  </si>
-  <si>
-    <t>rez_ESP_126</t>
-  </si>
-  <si>
-    <t>elc*ESP_0126</t>
-  </si>
-  <si>
-    <t>rez_ESP_127</t>
-  </si>
-  <si>
-    <t>elc*ESP_0127</t>
-  </si>
-  <si>
-    <t>rez_ESP_128</t>
-  </si>
-  <si>
-    <t>elc*ESP_0128</t>
-  </si>
-  <si>
-    <t>rez_ESP_129</t>
-  </si>
-  <si>
-    <t>elc*ESP_0129</t>
-  </si>
-  <si>
-    <t>rez_ESP_130</t>
-  </si>
-  <si>
-    <t>elc*ESP_0130</t>
-  </si>
-  <si>
-    <t>rez_ESP_131</t>
-  </si>
-  <si>
-    <t>elc*ESP_0131</t>
-  </si>
-  <si>
-    <t>rez_ESP_132</t>
-  </si>
-  <si>
-    <t>elc*ESP_0132</t>
-  </si>
-  <si>
-    <t>rez_ESP_133</t>
-  </si>
-  <si>
-    <t>elc*ESP_0133</t>
-  </si>
-  <si>
-    <t>rez_ESP_134</t>
-  </si>
-  <si>
-    <t>elc*ESP_0134</t>
-  </si>
-  <si>
-    <t>rez_ESP_135</t>
-  </si>
-  <si>
-    <t>elc*ESP_0135</t>
-  </si>
-  <si>
-    <t>rez_ESP_136</t>
-  </si>
-  <si>
-    <t>elc*ESP_0136</t>
-  </si>
-  <si>
-    <t>rez_ESP_137</t>
-  </si>
-  <si>
-    <t>elc*ESP_0137</t>
-  </si>
-  <si>
-    <t>rez_ESP_138</t>
-  </si>
-  <si>
-    <t>elc*ESP_0138</t>
-  </si>
-  <si>
-    <t>rez_ESP_139</t>
-  </si>
-  <si>
-    <t>elc*ESP_0139</t>
-  </si>
-  <si>
-    <t>rez_ESP_140</t>
-  </si>
-  <si>
-    <t>elc*ESP_0140</t>
-  </si>
-  <si>
-    <t>rez_ESP_141</t>
-  </si>
-  <si>
-    <t>elc*ESP_0141</t>
-  </si>
-  <si>
-    <t>rez_ESP_142</t>
-  </si>
-  <si>
-    <t>elc*ESP_0142</t>
-  </si>
-  <si>
-    <t>rez_ESP_143</t>
-  </si>
-  <si>
-    <t>elc*ESP_0143</t>
-  </si>
-  <si>
-    <t>rez_ESP_144</t>
-  </si>
-  <si>
-    <t>elc*ESP_0144</t>
-  </si>
-  <si>
-    <t>rez_ESP_145</t>
-  </si>
-  <si>
-    <t>elc*ESP_0145</t>
-  </si>
-  <si>
-    <t>rez_ESP_146</t>
-  </si>
-  <si>
-    <t>elc*ESP_0146</t>
-  </si>
-  <si>
-    <t>rez_ESP_147</t>
-  </si>
-  <si>
-    <t>elc*ESP_0147</t>
-  </si>
-  <si>
-    <t>rez_ESP_148</t>
-  </si>
-  <si>
-    <t>elc*ESP_0148</t>
-  </si>
-  <si>
-    <t>rez_ESP_149</t>
-  </si>
-  <si>
-    <t>elc*ESP_0149</t>
-  </si>
-  <si>
-    <t>rez_ESP_150</t>
-  </si>
-  <si>
-    <t>elc*ESP_0150</t>
-  </si>
-  <si>
-    <t>rez_ESP_151</t>
-  </si>
-  <si>
-    <t>elc*ESP_0151</t>
-  </si>
-  <si>
-    <t>rez_ESP_152</t>
-  </si>
-  <si>
-    <t>elc*ESP_0152</t>
-  </si>
-  <si>
-    <t>rez_ESP_153</t>
-  </si>
-  <si>
-    <t>elc*ESP_0153</t>
-  </si>
-  <si>
-    <t>rez_ESP_154</t>
-  </si>
-  <si>
-    <t>elc*ESP_0154</t>
-  </si>
-  <si>
-    <t>rez_ESP_155</t>
-  </si>
-  <si>
-    <t>elc*ESP_0155</t>
-  </si>
-  <si>
-    <t>rez_ESP_156</t>
-  </si>
-  <si>
-    <t>elc*ESP_0156</t>
-  </si>
-  <si>
-    <t>rez_ESP_157</t>
-  </si>
-  <si>
-    <t>elc*ESP_0157</t>
-  </si>
-  <si>
-    <t>rez_ESP_158</t>
-  </si>
-  <si>
-    <t>elc*ESP_0158</t>
-  </si>
-  <si>
-    <t>rez_ESP_159</t>
-  </si>
-  <si>
-    <t>elc*ESP_0159</t>
-  </si>
-  <si>
-    <t>rez_ESP_160</t>
-  </si>
-  <si>
-    <t>elc*ESP_0160</t>
-  </si>
-  <si>
-    <t>rez_ESP_161</t>
-  </si>
-  <si>
-    <t>elc*ESP_0161</t>
-  </si>
-  <si>
-    <t>rez_ESP_162</t>
-  </si>
-  <si>
-    <t>elc*ESP_0162</t>
-  </si>
-  <si>
-    <t>rez_ESP_163</t>
-  </si>
-  <si>
-    <t>elc*ESP_0163</t>
-  </si>
-  <si>
-    <t>rez_ESP_164</t>
-  </si>
-  <si>
-    <t>elc*ESP_0164</t>
-  </si>
-  <si>
-    <t>rez_ESP_165</t>
-  </si>
-  <si>
-    <t>elc*ESP_0165</t>
-  </si>
-  <si>
-    <t>rez_ESP_166</t>
-  </si>
-  <si>
-    <t>elc*ESP_0166</t>
-  </si>
-  <si>
-    <t>rez_ESP_167</t>
-  </si>
-  <si>
-    <t>elc*ESP_0167</t>
-  </si>
-  <si>
-    <t>rez_ESP_168</t>
-  </si>
-  <si>
-    <t>elc*ESP_0168</t>
-  </si>
-  <si>
-    <t>rez_ESP_169</t>
-  </si>
-  <si>
-    <t>elc*ESP_0169</t>
-  </si>
-  <si>
-    <t>rez_ESP_170</t>
-  </si>
-  <si>
-    <t>elc*ESP_0170</t>
-  </si>
-  <si>
-    <t>rez_ESP_171</t>
-  </si>
-  <si>
-    <t>elc*ESP_0171</t>
-  </si>
-  <si>
-    <t>rez_ESP_172</t>
-  </si>
-  <si>
-    <t>elc*ESP_0172</t>
-  </si>
-  <si>
-    <t>rez_ESP_173</t>
-  </si>
-  <si>
-    <t>elc*ESP_0173</t>
-  </si>
-  <si>
-    <t>rez_ESP_174</t>
-  </si>
-  <si>
-    <t>elc*ESP_0174</t>
-  </si>
-  <si>
-    <t>rez_ESP_175</t>
-  </si>
-  <si>
-    <t>elc*ESP_0175</t>
-  </si>
-  <si>
-    <t>rez_ESP_176</t>
-  </si>
-  <si>
-    <t>elc*ESP_0176</t>
-  </si>
-  <si>
-    <t>rez_ESP_177</t>
-  </si>
-  <si>
-    <t>elc*ESP_0177</t>
-  </si>
-  <si>
-    <t>rez_ESP_178</t>
-  </si>
-  <si>
-    <t>elc*ESP_0178</t>
-  </si>
-  <si>
-    <t>rez_ESP_179</t>
-  </si>
-  <si>
-    <t>elc*ESP_0179</t>
-  </si>
-  <si>
-    <t>rez_ESP_180</t>
-  </si>
-  <si>
-    <t>elc*ESP_0180</t>
-  </si>
-  <si>
-    <t>rez_ESP_181</t>
-  </si>
-  <si>
-    <t>elc*ESP_0181</t>
-  </si>
-  <si>
-    <t>rez_ESP_182</t>
-  </si>
-  <si>
-    <t>elc*ESP_0182</t>
-  </si>
-  <si>
-    <t>rez_ESP_183</t>
-  </si>
-  <si>
-    <t>elc*ESP_0183</t>
-  </si>
-  <si>
-    <t>rez_ESP_184</t>
-  </si>
-  <si>
-    <t>elc*ESP_0184</t>
-  </si>
-  <si>
-    <t>rez_ESP_185</t>
-  </si>
-  <si>
-    <t>elc*ESP_0185</t>
-  </si>
-  <si>
-    <t>rez_ESP_186</t>
-  </si>
-  <si>
-    <t>elc*ESP_0186</t>
-  </si>
-  <si>
-    <t>rez_ESP_187</t>
-  </si>
-  <si>
-    <t>elc*ESP_0187</t>
-  </si>
-  <si>
-    <t>rez_ESP_188</t>
-  </si>
-  <si>
-    <t>elc*ESP_0188</t>
-  </si>
-  <si>
-    <t>rez_ESP_189</t>
-  </si>
-  <si>
-    <t>elc*ESP_0189</t>
-  </si>
-  <si>
-    <t>rez_ESP_190</t>
-  </si>
-  <si>
-    <t>elc*ESP_0190</t>
-  </si>
-  <si>
-    <t>rez_ESP_191</t>
-  </si>
-  <si>
-    <t>elc*ESP_0191</t>
-  </si>
-  <si>
-    <t>rez_ESP_192</t>
-  </si>
-  <si>
-    <t>elc*ESP_0192</t>
-  </si>
-  <si>
-    <t>rez_ESP_193</t>
-  </si>
-  <si>
-    <t>elc*ESP_0193</t>
-  </si>
-  <si>
-    <t>rez_ESP_194</t>
-  </si>
-  <si>
-    <t>elc*ESP_0194</t>
-  </si>
-  <si>
-    <t>rez_ESP_195</t>
-  </si>
-  <si>
-    <t>elc*ESP_0195</t>
-  </si>
-  <si>
-    <t>rez_ESP_196</t>
-  </si>
-  <si>
-    <t>elc*ESP_0196</t>
-  </si>
-  <si>
-    <t>rez_ESP_197</t>
-  </si>
-  <si>
-    <t>elc*ESP_0197</t>
-  </si>
-  <si>
-    <t>rez_ESP_198</t>
-  </si>
-  <si>
-    <t>elc*ESP_0198</t>
-  </si>
-  <si>
-    <t>rez_ESP_199</t>
-  </si>
-  <si>
-    <t>elc*ESP_0199</t>
-  </si>
-  <si>
-    <t>rez_ESP_200</t>
-  </si>
-  <si>
-    <t>elc*ESP_0200</t>
-  </si>
-  <si>
-    <t>rez_ESP_201</t>
-  </si>
-  <si>
-    <t>elc*ESP_0201</t>
-  </si>
-  <si>
-    <t>rez_ESP_202</t>
-  </si>
-  <si>
-    <t>elc*ESP_0202</t>
-  </si>
-  <si>
-    <t>rez_ESP_203</t>
-  </si>
-  <si>
-    <t>elc*ESP_0203</t>
-  </si>
-  <si>
-    <t>rez_ESP_204</t>
-  </si>
-  <si>
-    <t>elc*ESP_0204</t>
-  </si>
-  <si>
-    <t>rez_ESP_205</t>
-  </si>
-  <si>
-    <t>elc*ESP_0205</t>
-  </si>
-  <si>
-    <t>rez_ESP_206</t>
-  </si>
-  <si>
-    <t>elc*ESP_0206</t>
-  </si>
-  <si>
-    <t>rez_ESP_207</t>
-  </si>
-  <si>
-    <t>elc*ESP_0207</t>
-  </si>
-  <si>
-    <t>rez_ESP_208</t>
-  </si>
-  <si>
-    <t>elc*ESP_0208</t>
-  </si>
-  <si>
-    <t>rez_ESP_209</t>
-  </si>
-  <si>
-    <t>elc*ESP_0209</t>
-  </si>
-  <si>
-    <t>rez_ESP_210</t>
-  </si>
-  <si>
-    <t>elc*ESP_0210</t>
-  </si>
-  <si>
-    <t>rez_ESP_211</t>
-  </si>
-  <si>
-    <t>elc*ESP_0211</t>
-  </si>
-  <si>
-    <t>rez_ESP_212</t>
-  </si>
-  <si>
-    <t>elc*ESP_0212</t>
-  </si>
-  <si>
-    <t>rez_ESP_213</t>
-  </si>
-  <si>
-    <t>elc*ESP_0213</t>
-  </si>
-  <si>
-    <t>rez_ESP_214</t>
-  </si>
-  <si>
-    <t>elc*ESP_0214</t>
-  </si>
-  <si>
-    <t>rez_ESP_215</t>
-  </si>
-  <si>
-    <t>elc*ESP_0215</t>
-  </si>
-  <si>
-    <t>rez_ESP_216</t>
-  </si>
-  <si>
-    <t>elc*ESP_0216</t>
-  </si>
-  <si>
-    <t>rez_ESP_217</t>
-  </si>
-  <si>
-    <t>elc*ESP_0217</t>
-  </si>
-  <si>
-    <t>rez_ESP_218</t>
-  </si>
-  <si>
-    <t>elc*ESP_0218</t>
-  </si>
-  <si>
-    <t>rez_ESP_219</t>
-  </si>
-  <si>
-    <t>elc*ESP_0219</t>
-  </si>
-  <si>
-    <t>rez_ESP_220</t>
-  </si>
-  <si>
-    <t>elc*ESP_0220</t>
-  </si>
-  <si>
-    <t>rez_ESP_221</t>
-  </si>
-  <si>
-    <t>elc*ESP_0221</t>
-  </si>
-  <si>
-    <t>rez_ESP_222</t>
-  </si>
-  <si>
-    <t>elc*ESP_0222</t>
-  </si>
-  <si>
-    <t>rez_ESP_223</t>
-  </si>
-  <si>
-    <t>elc*ESP_0223</t>
-  </si>
-  <si>
-    <t>rez_ESP_224</t>
-  </si>
-  <si>
-    <t>elc*ESP_0224</t>
-  </si>
-  <si>
-    <t>rez_ESP_225</t>
-  </si>
-  <si>
-    <t>elc*ESP_0225</t>
-  </si>
-  <si>
-    <t>rez_ESP_226</t>
-  </si>
-  <si>
-    <t>elc*ESP_0226</t>
-  </si>
-  <si>
-    <t>rez_ESP_227</t>
-  </si>
-  <si>
-    <t>elc*ESP_0227</t>
-  </si>
-  <si>
-    <t>rez_ESP_228</t>
-  </si>
-  <si>
-    <t>elc*ESP_0228</t>
-  </si>
-  <si>
-    <t>rez_ESP_229</t>
-  </si>
-  <si>
-    <t>elc*ESP_0229</t>
-  </si>
-  <si>
-    <t>rez_ESP_230</t>
-  </si>
-  <si>
-    <t>elc*ESP_0230</t>
-  </si>
-  <si>
-    <t>rez_ESP_231</t>
-  </si>
-  <si>
-    <t>elc*ESP_0231</t>
-  </si>
-  <si>
-    <t>rez_ESP_232</t>
-  </si>
-  <si>
-    <t>elc*ESP_0232</t>
-  </si>
-  <si>
-    <t>rez_ESP_233</t>
-  </si>
-  <si>
-    <t>elc*ESP_0233</t>
-  </si>
-  <si>
-    <t>rez_ESP_234</t>
-  </si>
-  <si>
-    <t>elc*ESP_0234</t>
-  </si>
-  <si>
-    <t>wof_ESP_38</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0038</t>
-  </si>
-  <si>
-    <t>wof_ESP_39</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0039</t>
-  </si>
-  <si>
-    <t>wof_ESP_48</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0048</t>
-  </si>
-  <si>
-    <t>wof_ESP_81</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0081</t>
-  </si>
-  <si>
-    <t>wof_ESP_82</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0082</t>
-  </si>
-  <si>
-    <t>wof_ESP_83</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0083</t>
-  </si>
-  <si>
-    <t>wof_ESP_91</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0091</t>
-  </si>
-  <si>
-    <t>wof_ESP_92</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0092</t>
-  </si>
-  <si>
-    <t>wof_ESP_93</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0093</t>
-  </si>
-  <si>
-    <t>wof_ESP_94</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0094</t>
-  </si>
-  <si>
-    <t>wof_ESP_95</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0095</t>
-  </si>
-  <si>
-    <t>wof_ESP_96</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0096</t>
-  </si>
-  <si>
-    <t>wof_ESP_102</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0102</t>
-  </si>
-  <si>
-    <t>wof_ESP_103</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0103</t>
-  </si>
-  <si>
-    <t>wof_ESP_105</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0105</t>
-  </si>
-  <si>
-    <t>wof_ESP_106</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0106</t>
-  </si>
-  <si>
-    <t>wof_ESP_107</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0107</t>
-  </si>
-  <si>
-    <t>wof_ESP_112</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0112</t>
-  </si>
-  <si>
-    <t>wof_ESP_113</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0113</t>
-  </si>
-  <si>
-    <t>wof_ESP_114</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0114</t>
-  </si>
-  <si>
-    <t>wof_ESP_119</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0119</t>
-  </si>
-  <si>
-    <t>wof_ESP_121</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0121</t>
-  </si>
-  <si>
-    <t>wof_ESP_122</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0122</t>
-  </si>
-  <si>
-    <t>wof_ESP_126</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0126</t>
-  </si>
-  <si>
-    <t>wof_ESP_127</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0127</t>
-  </si>
-  <si>
-    <t>wof_ESP_128</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0128</t>
-  </si>
-  <si>
-    <t>wof_ESP_129</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0129</t>
-  </si>
-  <si>
-    <t>wof_ESP_132</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0132</t>
-  </si>
-  <si>
-    <t>wof_ESP_133</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0133</t>
-  </si>
-  <si>
-    <t>wof_ESP_137</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0137</t>
-  </si>
-  <si>
-    <t>wof_ESP_138</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0138</t>
-  </si>
-  <si>
-    <t>wof_ESP_139</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0139</t>
-  </si>
-  <si>
-    <t>wof_ESP_140</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0140</t>
-  </si>
-  <si>
-    <t>wof_ESP_143</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0143</t>
-  </si>
-  <si>
-    <t>wof_ESP_144</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0144</t>
-  </si>
-  <si>
-    <t>wof_ESP_148</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0148</t>
-  </si>
-  <si>
-    <t>wof_ESP_149</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0149</t>
-  </si>
-  <si>
-    <t>wof_ESP_150</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0150</t>
-  </si>
-  <si>
-    <t>wof_ESP_153</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0153</t>
-  </si>
-  <si>
-    <t>wof_ESP_158</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0158</t>
-  </si>
-  <si>
-    <t>wof_ESP_160</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0160</t>
-  </si>
-  <si>
-    <t>wof_ESP_161</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0161</t>
-  </si>
-  <si>
-    <t>wof_ESP_164</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0164</t>
-  </si>
-  <si>
-    <t>wof_ESP_165</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0165</t>
-  </si>
-  <si>
-    <t>wof_ESP_166</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0166</t>
-  </si>
-  <si>
-    <t>wof_ESP_167</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0167</t>
-  </si>
-  <si>
-    <t>wof_ESP_168</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0168</t>
-  </si>
-  <si>
-    <t>wof_ESP_169</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0169</t>
-  </si>
-  <si>
-    <t>wof_ESP_172</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0172</t>
-  </si>
-  <si>
-    <t>wof_ESP_173</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0173</t>
-  </si>
-  <si>
-    <t>wof_ESP_174</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0174</t>
-  </si>
-  <si>
-    <t>wof_ESP_175</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0175</t>
-  </si>
-  <si>
-    <t>wof_ESP_176</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0176</t>
-  </si>
-  <si>
-    <t>wof_ESP_177</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0177</t>
-  </si>
-  <si>
-    <t>wof_ESP_180</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0180</t>
-  </si>
-  <si>
-    <t>wof_ESP_181</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0181</t>
-  </si>
-  <si>
-    <t>wof_ESP_182</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0182</t>
-  </si>
-  <si>
-    <t>wof_ESP_183</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0183</t>
-  </si>
-  <si>
-    <t>wof_ESP_184</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0184</t>
-  </si>
-  <si>
-    <t>wof_ESP_188</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0188</t>
-  </si>
-  <si>
-    <t>wof_ESP_189</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0189</t>
-  </si>
-  <si>
-    <t>wof_ESP_190</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0190</t>
-  </si>
-  <si>
-    <t>wof_ESP_191</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0191</t>
-  </si>
-  <si>
-    <t>wof_ESP_192</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0192</t>
-  </si>
-  <si>
-    <t>wof_ESP_196</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0196</t>
-  </si>
-  <si>
-    <t>wof_ESP_197</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0197</t>
-  </si>
-  <si>
-    <t>wof_ESP_198</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0198</t>
-  </si>
-  <si>
-    <t>wof_ESP_199</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0199</t>
-  </si>
-  <si>
-    <t>wof_ESP_200</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0200</t>
-  </si>
-  <si>
-    <t>wof_ESP_203</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0203</t>
-  </si>
-  <si>
-    <t>wof_ESP_204</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0204</t>
-  </si>
-  <si>
-    <t>wof_ESP_205</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0205</t>
-  </si>
-  <si>
-    <t>wof_ESP_206</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0206</t>
-  </si>
-  <si>
-    <t>wof_ESP_207</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0207</t>
-  </si>
-  <si>
-    <t>wof_ESP_208</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0208</t>
-  </si>
-  <si>
-    <t>wof_ESP_209</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0209</t>
-  </si>
-  <si>
-    <t>wof_ESP_210</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0210</t>
-  </si>
-  <si>
-    <t>wof_ESP_212</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0212</t>
-  </si>
-  <si>
-    <t>wof_ESP_213</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0213</t>
-  </si>
-  <si>
-    <t>wof_ESP_214</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0214</t>
-  </si>
-  <si>
-    <t>wof_ESP_215</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0215</t>
-  </si>
-  <si>
-    <t>wof_ESP_216</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0216</t>
-  </si>
-  <si>
-    <t>wof_ESP_217</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0217</t>
-  </si>
-  <si>
-    <t>wof_ESP_218</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0218</t>
-  </si>
-  <si>
-    <t>wof_ESP_220</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0220</t>
-  </si>
-  <si>
-    <t>wof_ESP_221</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0221</t>
-  </si>
-  <si>
-    <t>wof_ESP_222</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0222</t>
-  </si>
-  <si>
-    <t>wof_ESP_223</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0223</t>
-  </si>
-  <si>
-    <t>wof_ESP_224</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0224</t>
-  </si>
-  <si>
-    <t>wof_ESP_227</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0227</t>
-  </si>
-  <si>
-    <t>wof_ESP_231</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0231</t>
-  </si>
-  <si>
-    <t>wof_ESP_232</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0232</t>
-  </si>
-  <si>
-    <t>wof_ESP_233</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0233</t>
-  </si>
-  <si>
-    <t>wof_ESP_235</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0235</t>
-  </si>
-  <si>
-    <t>wof_ESP_236</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0236</t>
-  </si>
-  <si>
-    <t>wof_ESP_237</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0237</t>
-  </si>
-  <si>
-    <t>wof_ESP_238</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0238</t>
-  </si>
-  <si>
-    <t>wof_ESP_239</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0239</t>
-  </si>
-  <si>
-    <t>wof_ESP_240</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0240</t>
-  </si>
-  <si>
-    <t>wof_ESP_244</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0244</t>
-  </si>
-  <si>
-    <t>wof_ESP_245</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0245</t>
-  </si>
-  <si>
-    <t>wof_ESP_246</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0246</t>
-  </si>
-  <si>
-    <t>wof_ESP_247</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0247</t>
-  </si>
-  <si>
-    <t>wof_ESP_248</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0248</t>
-  </si>
-  <si>
-    <t>wof_ESP_249</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0249</t>
-  </si>
-  <si>
-    <t>wof_ESP_250</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0250</t>
-  </si>
-  <si>
-    <t>wof_ESP_252</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0252</t>
-  </si>
-  <si>
-    <t>wof_ESP_253</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0253</t>
-  </si>
-  <si>
-    <t>wof_ESP_254</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0254</t>
-  </si>
-  <si>
-    <t>wof_ESP_255</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0255</t>
-  </si>
-  <si>
-    <t>wof_ESP_256</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0256</t>
-  </si>
-  <si>
-    <t>wof_ESP_257</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0257</t>
-  </si>
-  <si>
-    <t>wof_ESP_258</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0258</t>
-  </si>
-  <si>
-    <t>wof_ESP_259</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0259</t>
-  </si>
-  <si>
-    <t>wof_ESP_262</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0262</t>
-  </si>
-  <si>
-    <t>wof_ESP_263</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0263</t>
-  </si>
-  <si>
-    <t>wof_ESP_264</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0264</t>
-  </si>
-  <si>
-    <t>wof_ESP_266</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0266</t>
-  </si>
-  <si>
-    <t>wof_ESP_267</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0267</t>
-  </si>
-  <si>
-    <t>wof_ESP_268</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0268</t>
-  </si>
-  <si>
-    <t>wof_ESP_271</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0271</t>
-  </si>
-  <si>
-    <t>wof_ESP_272</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0272</t>
-  </si>
-  <si>
-    <t>wof_ESP_273</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0273</t>
-  </si>
-  <si>
-    <t>wof_ESP_274</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0274</t>
-  </si>
-  <si>
-    <t>wof_ESP_276</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0276</t>
-  </si>
-  <si>
-    <t>wof_ESP_277</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0277</t>
-  </si>
-  <si>
-    <t>wof_ESP_278</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0278</t>
-  </si>
-  <si>
-    <t>wof_ESP_280</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0280</t>
-  </si>
-  <si>
-    <t>wof_ESP_281</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0281</t>
-  </si>
-  <si>
-    <t>wof_ESP_282</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0282</t>
-  </si>
-  <si>
-    <t>wof_ESP_283</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0283</t>
-  </si>
-  <si>
-    <t>wof_ESP_286</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0286</t>
-  </si>
-  <si>
-    <t>wof_ESP_287</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0287</t>
-  </si>
-  <si>
-    <t>wof_ESP_290</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0290</t>
-  </si>
-  <si>
-    <t>wof_ESP_291</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0291</t>
-  </si>
-  <si>
-    <t>wof_ESP_292</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0292</t>
-  </si>
-  <si>
-    <t>wof_ESP_293</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0293</t>
-  </si>
-  <si>
-    <t>wof_ESP_295</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0295</t>
-  </si>
-  <si>
-    <t>wof_ESP_296</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0296</t>
-  </si>
-  <si>
-    <t>wof_ESP_297</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0297</t>
-  </si>
-  <si>
-    <t>wof_ESP_298</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0298</t>
-  </si>
-  <si>
-    <t>wof_ESP_302</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0302</t>
-  </si>
-  <si>
-    <t>wof_ESP_303</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0303</t>
-  </si>
-  <si>
-    <t>wof_ESP_304</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0304</t>
-  </si>
-  <si>
-    <t>wof_ESP_307</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0307</t>
-  </si>
-  <si>
-    <t>wof_ESP_308</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0308</t>
-  </si>
-  <si>
-    <t>wof_ESP_309</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0309</t>
-  </si>
-  <si>
-    <t>wof_ESP_310</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0310</t>
-  </si>
-  <si>
-    <t>wof_ESP_315</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0315</t>
-  </si>
-  <si>
-    <t>wof_ESP_316</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0316</t>
-  </si>
-  <si>
-    <t>wof_ESP_320</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0320</t>
-  </si>
-  <si>
-    <t>wof_ESP_321</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0321</t>
-  </si>
-  <si>
-    <t>wof_ESP_322</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0322</t>
-  </si>
-  <si>
-    <t>wof_ESP_326</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0326</t>
-  </si>
-  <si>
-    <t>wof_ESP_327</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0327</t>
-  </si>
-  <si>
-    <t>wof_ESP_332</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0332</t>
-  </si>
-  <si>
-    <t>wof_ESP_333</t>
-  </si>
-  <si>
-    <t>elc_wof*ESP_0333</t>
+    <t>rez_spv_001</t>
+  </si>
+  <si>
+    <t>elc_spv_001</t>
+  </si>
+  <si>
+    <t>rez_spv_002</t>
+  </si>
+  <si>
+    <t>elc_spv_002</t>
+  </si>
+  <si>
+    <t>rez_spv_003</t>
+  </si>
+  <si>
+    <t>elc_spv_003</t>
+  </si>
+  <si>
+    <t>rez_spv_004</t>
+  </si>
+  <si>
+    <t>elc_spv_004</t>
+  </si>
+  <si>
+    <t>rez_spv_005</t>
+  </si>
+  <si>
+    <t>elc_spv_005</t>
+  </si>
+  <si>
+    <t>rez_spv_006</t>
+  </si>
+  <si>
+    <t>elc_spv_006</t>
+  </si>
+  <si>
+    <t>rez_spv_007</t>
+  </si>
+  <si>
+    <t>elc_spv_007</t>
+  </si>
+  <si>
+    <t>rez_spv_008</t>
+  </si>
+  <si>
+    <t>elc_spv_008</t>
+  </si>
+  <si>
+    <t>rez_spv_009</t>
+  </si>
+  <si>
+    <t>elc_spv_009</t>
+  </si>
+  <si>
+    <t>rez_spv_010</t>
+  </si>
+  <si>
+    <t>elc_spv_010</t>
+  </si>
+  <si>
+    <t>rez_spv_011</t>
+  </si>
+  <si>
+    <t>elc_spv_011</t>
+  </si>
+  <si>
+    <t>rez_spv_012</t>
+  </si>
+  <si>
+    <t>elc_spv_012</t>
+  </si>
+  <si>
+    <t>rez_spv_013</t>
+  </si>
+  <si>
+    <t>elc_spv_013</t>
+  </si>
+  <si>
+    <t>rez_spv_014</t>
+  </si>
+  <si>
+    <t>elc_spv_014</t>
+  </si>
+  <si>
+    <t>rez_spv_015</t>
+  </si>
+  <si>
+    <t>elc_spv_015</t>
+  </si>
+  <si>
+    <t>rez_spv_016</t>
+  </si>
+  <si>
+    <t>elc_spv_016</t>
+  </si>
+  <si>
+    <t>rez_spv_017</t>
+  </si>
+  <si>
+    <t>elc_spv_017</t>
+  </si>
+  <si>
+    <t>rez_spv_018</t>
+  </si>
+  <si>
+    <t>elc_spv_018</t>
+  </si>
+  <si>
+    <t>rez_spv_019</t>
+  </si>
+  <si>
+    <t>elc_spv_019</t>
+  </si>
+  <si>
+    <t>rez_spv_020</t>
+  </si>
+  <si>
+    <t>elc_spv_020</t>
+  </si>
+  <si>
+    <t>rez_spv_021</t>
+  </si>
+  <si>
+    <t>elc_spv_021</t>
+  </si>
+  <si>
+    <t>rez_spv_022</t>
+  </si>
+  <si>
+    <t>elc_spv_022</t>
+  </si>
+  <si>
+    <t>rez_spv_023</t>
+  </si>
+  <si>
+    <t>elc_spv_023</t>
+  </si>
+  <si>
+    <t>rez_spv_024</t>
+  </si>
+  <si>
+    <t>elc_spv_024</t>
+  </si>
+  <si>
+    <t>rez_spv_025</t>
+  </si>
+  <si>
+    <t>elc_spv_025</t>
+  </si>
+  <si>
+    <t>rez_spv_026</t>
+  </si>
+  <si>
+    <t>elc_spv_026</t>
+  </si>
+  <si>
+    <t>rez_won_001</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>rez_won_002</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>rez_won_003</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>rez_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>rez_won_005</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>rez_won_006</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>rez_won_007</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>rez_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>rez_won_009</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>rez_won_010</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>rez_won_011</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>rez_won_012</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>rez_won_013</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>rez_won_014</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>rez_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>rez_won_016</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>rez_won_017</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>rez_won_018</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>rez_won_019</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>rez_won_020</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>rez_won_021</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>rez_won_022</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>rez_won_023</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>rez_won_024</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>rez_won_025</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>rez_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>rez_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>rez_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>rez_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>rez_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>rez_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>rez_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>rez_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>rez_wof_009</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>rez_wof_010</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>rez_wof_011</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>rez_wof_012</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>rez_wof_013</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>rez_wof_014</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>rez_wof_015</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>rez_wof_016</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>rez_wof_017</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>rez_wof_018</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
   </si>
 </sst>
 </file>
@@ -5195,8 +3257,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4274FBF-9631-49AC-A814-63419B16AB9A}">
-  <dimension ref="B9:E678"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA4A7D14-C4FD-42F9-8B11-DA0DAF1CAE8B}">
+  <dimension ref="B9:E355"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
@@ -10045,4528 +8107,6 @@
         <v>793</v>
       </c>
       <c r="E355" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="356" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B356" t="s">
-        <v>794</v>
-      </c>
-      <c r="C356" t="s">
-        <v>795</v>
-      </c>
-      <c r="D356" t="s">
-        <v>795</v>
-      </c>
-      <c r="E356" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="357" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B357" t="s">
-        <v>796</v>
-      </c>
-      <c r="C357" t="s">
-        <v>797</v>
-      </c>
-      <c r="D357" t="s">
-        <v>797</v>
-      </c>
-      <c r="E357" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="358" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B358" t="s">
-        <v>798</v>
-      </c>
-      <c r="C358" t="s">
-        <v>799</v>
-      </c>
-      <c r="D358" t="s">
-        <v>799</v>
-      </c>
-      <c r="E358" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="359" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B359" t="s">
-        <v>800</v>
-      </c>
-      <c r="C359" t="s">
-        <v>801</v>
-      </c>
-      <c r="D359" t="s">
-        <v>801</v>
-      </c>
-      <c r="E359" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="360" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B360" t="s">
-        <v>802</v>
-      </c>
-      <c r="C360" t="s">
-        <v>803</v>
-      </c>
-      <c r="D360" t="s">
-        <v>803</v>
-      </c>
-      <c r="E360" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="361" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B361" t="s">
-        <v>804</v>
-      </c>
-      <c r="C361" t="s">
-        <v>805</v>
-      </c>
-      <c r="D361" t="s">
-        <v>805</v>
-      </c>
-      <c r="E361" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="362" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B362" t="s">
-        <v>806</v>
-      </c>
-      <c r="C362" t="s">
-        <v>807</v>
-      </c>
-      <c r="D362" t="s">
-        <v>807</v>
-      </c>
-      <c r="E362" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="363" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B363" t="s">
-        <v>808</v>
-      </c>
-      <c r="C363" t="s">
-        <v>809</v>
-      </c>
-      <c r="D363" t="s">
-        <v>809</v>
-      </c>
-      <c r="E363" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="364" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B364" t="s">
-        <v>810</v>
-      </c>
-      <c r="C364" t="s">
-        <v>811</v>
-      </c>
-      <c r="D364" t="s">
-        <v>811</v>
-      </c>
-      <c r="E364" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="365" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B365" t="s">
-        <v>812</v>
-      </c>
-      <c r="C365" t="s">
-        <v>813</v>
-      </c>
-      <c r="D365" t="s">
-        <v>813</v>
-      </c>
-      <c r="E365" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="366" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B366" t="s">
-        <v>814</v>
-      </c>
-      <c r="C366" t="s">
-        <v>815</v>
-      </c>
-      <c r="D366" t="s">
-        <v>815</v>
-      </c>
-      <c r="E366" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="367" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B367" t="s">
-        <v>816</v>
-      </c>
-      <c r="C367" t="s">
-        <v>817</v>
-      </c>
-      <c r="D367" t="s">
-        <v>817</v>
-      </c>
-      <c r="E367" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="368" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B368" t="s">
-        <v>818</v>
-      </c>
-      <c r="C368" t="s">
-        <v>819</v>
-      </c>
-      <c r="D368" t="s">
-        <v>819</v>
-      </c>
-      <c r="E368" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="369" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B369" t="s">
-        <v>820</v>
-      </c>
-      <c r="C369" t="s">
-        <v>821</v>
-      </c>
-      <c r="D369" t="s">
-        <v>821</v>
-      </c>
-      <c r="E369" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="370" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B370" t="s">
-        <v>822</v>
-      </c>
-      <c r="C370" t="s">
-        <v>823</v>
-      </c>
-      <c r="D370" t="s">
-        <v>823</v>
-      </c>
-      <c r="E370" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="371" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B371" t="s">
-        <v>824</v>
-      </c>
-      <c r="C371" t="s">
-        <v>825</v>
-      </c>
-      <c r="D371" t="s">
-        <v>825</v>
-      </c>
-      <c r="E371" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="372" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B372" t="s">
-        <v>826</v>
-      </c>
-      <c r="C372" t="s">
-        <v>827</v>
-      </c>
-      <c r="D372" t="s">
-        <v>827</v>
-      </c>
-      <c r="E372" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="373" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B373" t="s">
-        <v>828</v>
-      </c>
-      <c r="C373" t="s">
-        <v>829</v>
-      </c>
-      <c r="D373" t="s">
-        <v>829</v>
-      </c>
-      <c r="E373" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="374" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B374" t="s">
-        <v>830</v>
-      </c>
-      <c r="C374" t="s">
-        <v>831</v>
-      </c>
-      <c r="D374" t="s">
-        <v>831</v>
-      </c>
-      <c r="E374" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="375" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B375" t="s">
-        <v>832</v>
-      </c>
-      <c r="C375" t="s">
-        <v>833</v>
-      </c>
-      <c r="D375" t="s">
-        <v>833</v>
-      </c>
-      <c r="E375" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="376" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B376" t="s">
-        <v>834</v>
-      </c>
-      <c r="C376" t="s">
-        <v>835</v>
-      </c>
-      <c r="D376" t="s">
-        <v>835</v>
-      </c>
-      <c r="E376" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="377" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B377" t="s">
-        <v>836</v>
-      </c>
-      <c r="C377" t="s">
-        <v>837</v>
-      </c>
-      <c r="D377" t="s">
-        <v>837</v>
-      </c>
-      <c r="E377" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="378" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B378" t="s">
-        <v>838</v>
-      </c>
-      <c r="C378" t="s">
-        <v>839</v>
-      </c>
-      <c r="D378" t="s">
-        <v>839</v>
-      </c>
-      <c r="E378" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="379" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B379" t="s">
-        <v>840</v>
-      </c>
-      <c r="C379" t="s">
-        <v>841</v>
-      </c>
-      <c r="D379" t="s">
-        <v>841</v>
-      </c>
-      <c r="E379" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="380" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B380" t="s">
-        <v>842</v>
-      </c>
-      <c r="C380" t="s">
-        <v>843</v>
-      </c>
-      <c r="D380" t="s">
-        <v>843</v>
-      </c>
-      <c r="E380" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="381" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B381" t="s">
-        <v>844</v>
-      </c>
-      <c r="C381" t="s">
-        <v>845</v>
-      </c>
-      <c r="D381" t="s">
-        <v>845</v>
-      </c>
-      <c r="E381" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="382" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B382" t="s">
-        <v>846</v>
-      </c>
-      <c r="C382" t="s">
-        <v>847</v>
-      </c>
-      <c r="D382" t="s">
-        <v>847</v>
-      </c>
-      <c r="E382" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="383" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B383" t="s">
-        <v>848</v>
-      </c>
-      <c r="C383" t="s">
-        <v>849</v>
-      </c>
-      <c r="D383" t="s">
-        <v>849</v>
-      </c>
-      <c r="E383" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="384" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B384" t="s">
-        <v>850</v>
-      </c>
-      <c r="C384" t="s">
-        <v>851</v>
-      </c>
-      <c r="D384" t="s">
-        <v>851</v>
-      </c>
-      <c r="E384" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="385" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B385" t="s">
-        <v>852</v>
-      </c>
-      <c r="C385" t="s">
-        <v>853</v>
-      </c>
-      <c r="D385" t="s">
-        <v>853</v>
-      </c>
-      <c r="E385" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="386" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B386" t="s">
-        <v>854</v>
-      </c>
-      <c r="C386" t="s">
-        <v>855</v>
-      </c>
-      <c r="D386" t="s">
-        <v>855</v>
-      </c>
-      <c r="E386" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="387" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B387" t="s">
-        <v>856</v>
-      </c>
-      <c r="C387" t="s">
-        <v>857</v>
-      </c>
-      <c r="D387" t="s">
-        <v>857</v>
-      </c>
-      <c r="E387" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="388" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B388" t="s">
-        <v>858</v>
-      </c>
-      <c r="C388" t="s">
-        <v>859</v>
-      </c>
-      <c r="D388" t="s">
-        <v>859</v>
-      </c>
-      <c r="E388" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="389" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B389" t="s">
-        <v>860</v>
-      </c>
-      <c r="C389" t="s">
-        <v>861</v>
-      </c>
-      <c r="D389" t="s">
-        <v>861</v>
-      </c>
-      <c r="E389" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="390" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B390" t="s">
-        <v>862</v>
-      </c>
-      <c r="C390" t="s">
-        <v>863</v>
-      </c>
-      <c r="D390" t="s">
-        <v>863</v>
-      </c>
-      <c r="E390" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="391" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B391" t="s">
-        <v>864</v>
-      </c>
-      <c r="C391" t="s">
-        <v>865</v>
-      </c>
-      <c r="D391" t="s">
-        <v>865</v>
-      </c>
-      <c r="E391" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="392" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B392" t="s">
-        <v>866</v>
-      </c>
-      <c r="C392" t="s">
-        <v>867</v>
-      </c>
-      <c r="D392" t="s">
-        <v>867</v>
-      </c>
-      <c r="E392" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="393" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B393" t="s">
-        <v>868</v>
-      </c>
-      <c r="C393" t="s">
-        <v>869</v>
-      </c>
-      <c r="D393" t="s">
-        <v>869</v>
-      </c>
-      <c r="E393" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="394" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B394" t="s">
-        <v>870</v>
-      </c>
-      <c r="C394" t="s">
-        <v>871</v>
-      </c>
-      <c r="D394" t="s">
-        <v>871</v>
-      </c>
-      <c r="E394" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="395" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B395" t="s">
-        <v>872</v>
-      </c>
-      <c r="C395" t="s">
-        <v>873</v>
-      </c>
-      <c r="D395" t="s">
-        <v>873</v>
-      </c>
-      <c r="E395" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="396" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B396" t="s">
-        <v>874</v>
-      </c>
-      <c r="C396" t="s">
-        <v>875</v>
-      </c>
-      <c r="D396" t="s">
-        <v>875</v>
-      </c>
-      <c r="E396" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="397" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B397" t="s">
-        <v>876</v>
-      </c>
-      <c r="C397" t="s">
-        <v>877</v>
-      </c>
-      <c r="D397" t="s">
-        <v>877</v>
-      </c>
-      <c r="E397" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="398" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B398" t="s">
-        <v>878</v>
-      </c>
-      <c r="C398" t="s">
-        <v>879</v>
-      </c>
-      <c r="D398" t="s">
-        <v>879</v>
-      </c>
-      <c r="E398" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="399" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B399" t="s">
-        <v>880</v>
-      </c>
-      <c r="C399" t="s">
-        <v>881</v>
-      </c>
-      <c r="D399" t="s">
-        <v>881</v>
-      </c>
-      <c r="E399" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="400" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B400" t="s">
-        <v>882</v>
-      </c>
-      <c r="C400" t="s">
-        <v>883</v>
-      </c>
-      <c r="D400" t="s">
-        <v>883</v>
-      </c>
-      <c r="E400" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="401" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B401" t="s">
-        <v>884</v>
-      </c>
-      <c r="C401" t="s">
-        <v>885</v>
-      </c>
-      <c r="D401" t="s">
-        <v>885</v>
-      </c>
-      <c r="E401" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="402" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B402" t="s">
-        <v>886</v>
-      </c>
-      <c r="C402" t="s">
-        <v>887</v>
-      </c>
-      <c r="D402" t="s">
-        <v>887</v>
-      </c>
-      <c r="E402" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="403" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B403" t="s">
-        <v>888</v>
-      </c>
-      <c r="C403" t="s">
-        <v>889</v>
-      </c>
-      <c r="D403" t="s">
-        <v>889</v>
-      </c>
-      <c r="E403" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="404" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B404" t="s">
-        <v>890</v>
-      </c>
-      <c r="C404" t="s">
-        <v>891</v>
-      </c>
-      <c r="D404" t="s">
-        <v>891</v>
-      </c>
-      <c r="E404" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="405" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B405" t="s">
-        <v>892</v>
-      </c>
-      <c r="C405" t="s">
-        <v>893</v>
-      </c>
-      <c r="D405" t="s">
-        <v>893</v>
-      </c>
-      <c r="E405" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="406" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B406" t="s">
-        <v>894</v>
-      </c>
-      <c r="C406" t="s">
-        <v>895</v>
-      </c>
-      <c r="D406" t="s">
-        <v>895</v>
-      </c>
-      <c r="E406" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="407" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B407" t="s">
-        <v>896</v>
-      </c>
-      <c r="C407" t="s">
-        <v>897</v>
-      </c>
-      <c r="D407" t="s">
-        <v>897</v>
-      </c>
-      <c r="E407" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="408" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B408" t="s">
-        <v>898</v>
-      </c>
-      <c r="C408" t="s">
-        <v>899</v>
-      </c>
-      <c r="D408" t="s">
-        <v>899</v>
-      </c>
-      <c r="E408" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="409" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B409" t="s">
-        <v>900</v>
-      </c>
-      <c r="C409" t="s">
-        <v>901</v>
-      </c>
-      <c r="D409" t="s">
-        <v>901</v>
-      </c>
-      <c r="E409" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="410" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B410" t="s">
-        <v>902</v>
-      </c>
-      <c r="C410" t="s">
-        <v>903</v>
-      </c>
-      <c r="D410" t="s">
-        <v>903</v>
-      </c>
-      <c r="E410" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="411" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B411" t="s">
-        <v>904</v>
-      </c>
-      <c r="C411" t="s">
-        <v>905</v>
-      </c>
-      <c r="D411" t="s">
-        <v>905</v>
-      </c>
-      <c r="E411" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="412" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B412" t="s">
-        <v>906</v>
-      </c>
-      <c r="C412" t="s">
-        <v>907</v>
-      </c>
-      <c r="D412" t="s">
-        <v>907</v>
-      </c>
-      <c r="E412" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="413" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B413" t="s">
-        <v>908</v>
-      </c>
-      <c r="C413" t="s">
-        <v>909</v>
-      </c>
-      <c r="D413" t="s">
-        <v>909</v>
-      </c>
-      <c r="E413" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="414" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B414" t="s">
-        <v>910</v>
-      </c>
-      <c r="C414" t="s">
-        <v>911</v>
-      </c>
-      <c r="D414" t="s">
-        <v>911</v>
-      </c>
-      <c r="E414" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="415" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B415" t="s">
-        <v>912</v>
-      </c>
-      <c r="C415" t="s">
-        <v>913</v>
-      </c>
-      <c r="D415" t="s">
-        <v>913</v>
-      </c>
-      <c r="E415" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="416" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B416" t="s">
-        <v>914</v>
-      </c>
-      <c r="C416" t="s">
-        <v>915</v>
-      </c>
-      <c r="D416" t="s">
-        <v>915</v>
-      </c>
-      <c r="E416" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="417" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B417" t="s">
-        <v>916</v>
-      </c>
-      <c r="C417" t="s">
-        <v>917</v>
-      </c>
-      <c r="D417" t="s">
-        <v>917</v>
-      </c>
-      <c r="E417" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="418" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B418" t="s">
-        <v>918</v>
-      </c>
-      <c r="C418" t="s">
-        <v>919</v>
-      </c>
-      <c r="D418" t="s">
-        <v>919</v>
-      </c>
-      <c r="E418" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="419" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B419" t="s">
-        <v>920</v>
-      </c>
-      <c r="C419" t="s">
-        <v>921</v>
-      </c>
-      <c r="D419" t="s">
-        <v>921</v>
-      </c>
-      <c r="E419" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="420" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B420" t="s">
-        <v>922</v>
-      </c>
-      <c r="C420" t="s">
-        <v>923</v>
-      </c>
-      <c r="D420" t="s">
-        <v>923</v>
-      </c>
-      <c r="E420" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="421" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B421" t="s">
-        <v>924</v>
-      </c>
-      <c r="C421" t="s">
-        <v>925</v>
-      </c>
-      <c r="D421" t="s">
-        <v>925</v>
-      </c>
-      <c r="E421" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="422" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B422" t="s">
-        <v>926</v>
-      </c>
-      <c r="C422" t="s">
-        <v>927</v>
-      </c>
-      <c r="D422" t="s">
-        <v>927</v>
-      </c>
-      <c r="E422" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="423" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B423" t="s">
-        <v>928</v>
-      </c>
-      <c r="C423" t="s">
-        <v>929</v>
-      </c>
-      <c r="D423" t="s">
-        <v>929</v>
-      </c>
-      <c r="E423" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="424" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B424" t="s">
-        <v>930</v>
-      </c>
-      <c r="C424" t="s">
-        <v>931</v>
-      </c>
-      <c r="D424" t="s">
-        <v>931</v>
-      </c>
-      <c r="E424" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="425" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B425" t="s">
-        <v>932</v>
-      </c>
-      <c r="C425" t="s">
-        <v>933</v>
-      </c>
-      <c r="D425" t="s">
-        <v>933</v>
-      </c>
-      <c r="E425" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="426" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B426" t="s">
-        <v>934</v>
-      </c>
-      <c r="C426" t="s">
-        <v>935</v>
-      </c>
-      <c r="D426" t="s">
-        <v>935</v>
-      </c>
-      <c r="E426" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="427" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B427" t="s">
-        <v>936</v>
-      </c>
-      <c r="C427" t="s">
-        <v>937</v>
-      </c>
-      <c r="D427" t="s">
-        <v>937</v>
-      </c>
-      <c r="E427" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="428" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B428" t="s">
-        <v>938</v>
-      </c>
-      <c r="C428" t="s">
-        <v>939</v>
-      </c>
-      <c r="D428" t="s">
-        <v>939</v>
-      </c>
-      <c r="E428" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="429" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B429" t="s">
-        <v>940</v>
-      </c>
-      <c r="C429" t="s">
-        <v>941</v>
-      </c>
-      <c r="D429" t="s">
-        <v>941</v>
-      </c>
-      <c r="E429" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="430" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B430" t="s">
-        <v>942</v>
-      </c>
-      <c r="C430" t="s">
-        <v>943</v>
-      </c>
-      <c r="D430" t="s">
-        <v>943</v>
-      </c>
-      <c r="E430" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="431" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B431" t="s">
-        <v>944</v>
-      </c>
-      <c r="C431" t="s">
-        <v>945</v>
-      </c>
-      <c r="D431" t="s">
-        <v>945</v>
-      </c>
-      <c r="E431" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="432" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B432" t="s">
-        <v>946</v>
-      </c>
-      <c r="C432" t="s">
-        <v>947</v>
-      </c>
-      <c r="D432" t="s">
-        <v>947</v>
-      </c>
-      <c r="E432" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="433" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B433" t="s">
-        <v>948</v>
-      </c>
-      <c r="C433" t="s">
-        <v>949</v>
-      </c>
-      <c r="D433" t="s">
-        <v>949</v>
-      </c>
-      <c r="E433" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="434" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B434" t="s">
-        <v>950</v>
-      </c>
-      <c r="C434" t="s">
-        <v>951</v>
-      </c>
-      <c r="D434" t="s">
-        <v>951</v>
-      </c>
-      <c r="E434" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="435" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B435" t="s">
-        <v>952</v>
-      </c>
-      <c r="C435" t="s">
-        <v>953</v>
-      </c>
-      <c r="D435" t="s">
-        <v>953</v>
-      </c>
-      <c r="E435" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="436" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B436" t="s">
-        <v>954</v>
-      </c>
-      <c r="C436" t="s">
-        <v>955</v>
-      </c>
-      <c r="D436" t="s">
-        <v>955</v>
-      </c>
-      <c r="E436" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="437" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B437" t="s">
-        <v>956</v>
-      </c>
-      <c r="C437" t="s">
-        <v>957</v>
-      </c>
-      <c r="D437" t="s">
-        <v>957</v>
-      </c>
-      <c r="E437" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="438" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B438" t="s">
-        <v>958</v>
-      </c>
-      <c r="C438" t="s">
-        <v>959</v>
-      </c>
-      <c r="D438" t="s">
-        <v>959</v>
-      </c>
-      <c r="E438" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="439" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B439" t="s">
-        <v>960</v>
-      </c>
-      <c r="C439" t="s">
-        <v>961</v>
-      </c>
-      <c r="D439" t="s">
-        <v>961</v>
-      </c>
-      <c r="E439" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="440" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B440" t="s">
-        <v>962</v>
-      </c>
-      <c r="C440" t="s">
-        <v>963</v>
-      </c>
-      <c r="D440" t="s">
-        <v>963</v>
-      </c>
-      <c r="E440" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="441" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B441" t="s">
-        <v>964</v>
-      </c>
-      <c r="C441" t="s">
-        <v>965</v>
-      </c>
-      <c r="D441" t="s">
-        <v>965</v>
-      </c>
-      <c r="E441" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="442" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B442" t="s">
-        <v>966</v>
-      </c>
-      <c r="C442" t="s">
-        <v>967</v>
-      </c>
-      <c r="D442" t="s">
-        <v>967</v>
-      </c>
-      <c r="E442" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="443" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B443" t="s">
-        <v>968</v>
-      </c>
-      <c r="C443" t="s">
-        <v>969</v>
-      </c>
-      <c r="D443" t="s">
-        <v>969</v>
-      </c>
-      <c r="E443" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="444" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B444" t="s">
-        <v>970</v>
-      </c>
-      <c r="C444" t="s">
-        <v>971</v>
-      </c>
-      <c r="D444" t="s">
-        <v>971</v>
-      </c>
-      <c r="E444" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="445" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B445" t="s">
-        <v>972</v>
-      </c>
-      <c r="C445" t="s">
-        <v>973</v>
-      </c>
-      <c r="D445" t="s">
-        <v>973</v>
-      </c>
-      <c r="E445" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="446" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B446" t="s">
-        <v>974</v>
-      </c>
-      <c r="C446" t="s">
-        <v>975</v>
-      </c>
-      <c r="D446" t="s">
-        <v>975</v>
-      </c>
-      <c r="E446" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="447" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B447" t="s">
-        <v>976</v>
-      </c>
-      <c r="C447" t="s">
-        <v>977</v>
-      </c>
-      <c r="D447" t="s">
-        <v>977</v>
-      </c>
-      <c r="E447" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="448" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B448" t="s">
-        <v>978</v>
-      </c>
-      <c r="C448" t="s">
-        <v>979</v>
-      </c>
-      <c r="D448" t="s">
-        <v>979</v>
-      </c>
-      <c r="E448" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="449" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B449" t="s">
-        <v>980</v>
-      </c>
-      <c r="C449" t="s">
-        <v>981</v>
-      </c>
-      <c r="D449" t="s">
-        <v>981</v>
-      </c>
-      <c r="E449" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="450" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B450" t="s">
-        <v>982</v>
-      </c>
-      <c r="C450" t="s">
-        <v>983</v>
-      </c>
-      <c r="D450" t="s">
-        <v>983</v>
-      </c>
-      <c r="E450" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="451" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B451" t="s">
-        <v>984</v>
-      </c>
-      <c r="C451" t="s">
-        <v>985</v>
-      </c>
-      <c r="D451" t="s">
-        <v>985</v>
-      </c>
-      <c r="E451" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="452" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B452" t="s">
-        <v>986</v>
-      </c>
-      <c r="C452" t="s">
-        <v>987</v>
-      </c>
-      <c r="D452" t="s">
-        <v>987</v>
-      </c>
-      <c r="E452" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="453" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B453" t="s">
-        <v>988</v>
-      </c>
-      <c r="C453" t="s">
-        <v>989</v>
-      </c>
-      <c r="D453" t="s">
-        <v>989</v>
-      </c>
-      <c r="E453" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="454" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B454" t="s">
-        <v>990</v>
-      </c>
-      <c r="C454" t="s">
-        <v>991</v>
-      </c>
-      <c r="D454" t="s">
-        <v>991</v>
-      </c>
-      <c r="E454" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="455" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B455" t="s">
-        <v>992</v>
-      </c>
-      <c r="C455" t="s">
-        <v>993</v>
-      </c>
-      <c r="D455" t="s">
-        <v>993</v>
-      </c>
-      <c r="E455" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="456" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B456" t="s">
-        <v>994</v>
-      </c>
-      <c r="C456" t="s">
-        <v>995</v>
-      </c>
-      <c r="D456" t="s">
-        <v>995</v>
-      </c>
-      <c r="E456" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="457" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B457" t="s">
-        <v>996</v>
-      </c>
-      <c r="C457" t="s">
-        <v>997</v>
-      </c>
-      <c r="D457" t="s">
-        <v>997</v>
-      </c>
-      <c r="E457" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="458" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B458" t="s">
-        <v>998</v>
-      </c>
-      <c r="C458" t="s">
-        <v>999</v>
-      </c>
-      <c r="D458" t="s">
-        <v>999</v>
-      </c>
-      <c r="E458" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="459" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B459" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C459" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D459" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E459" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="460" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B460" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C460" t="s">
-        <v>1003</v>
-      </c>
-      <c r="D460" t="s">
-        <v>1003</v>
-      </c>
-      <c r="E460" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="461" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B461" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C461" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D461" t="s">
-        <v>1005</v>
-      </c>
-      <c r="E461" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="462" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B462" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C462" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D462" t="s">
-        <v>1007</v>
-      </c>
-      <c r="E462" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="463" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B463" t="s">
-        <v>1008</v>
-      </c>
-      <c r="C463" t="s">
-        <v>1009</v>
-      </c>
-      <c r="D463" t="s">
-        <v>1009</v>
-      </c>
-      <c r="E463" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="464" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B464" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C464" t="s">
-        <v>1011</v>
-      </c>
-      <c r="D464" t="s">
-        <v>1011</v>
-      </c>
-      <c r="E464" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="465" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B465" t="s">
-        <v>1012</v>
-      </c>
-      <c r="C465" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D465" t="s">
-        <v>1013</v>
-      </c>
-      <c r="E465" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="466" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B466" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C466" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D466" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E466" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="467" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B467" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C467" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D467" t="s">
-        <v>1017</v>
-      </c>
-      <c r="E467" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="468" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B468" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C468" t="s">
-        <v>1019</v>
-      </c>
-      <c r="D468" t="s">
-        <v>1019</v>
-      </c>
-      <c r="E468" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="469" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B469" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C469" t="s">
-        <v>1021</v>
-      </c>
-      <c r="D469" t="s">
-        <v>1021</v>
-      </c>
-      <c r="E469" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="470" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B470" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C470" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D470" t="s">
-        <v>1023</v>
-      </c>
-      <c r="E470" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="471" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B471" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C471" t="s">
-        <v>1025</v>
-      </c>
-      <c r="D471" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E471" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="472" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B472" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C472" t="s">
-        <v>1027</v>
-      </c>
-      <c r="D472" t="s">
-        <v>1027</v>
-      </c>
-      <c r="E472" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="473" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B473" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C473" t="s">
-        <v>1029</v>
-      </c>
-      <c r="D473" t="s">
-        <v>1029</v>
-      </c>
-      <c r="E473" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="474" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B474" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C474" t="s">
-        <v>1031</v>
-      </c>
-      <c r="D474" t="s">
-        <v>1031</v>
-      </c>
-      <c r="E474" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="475" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B475" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C475" t="s">
-        <v>1033</v>
-      </c>
-      <c r="D475" t="s">
-        <v>1033</v>
-      </c>
-      <c r="E475" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="476" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B476" t="s">
-        <v>1034</v>
-      </c>
-      <c r="C476" t="s">
-        <v>1035</v>
-      </c>
-      <c r="D476" t="s">
-        <v>1035</v>
-      </c>
-      <c r="E476" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="477" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B477" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C477" t="s">
-        <v>1037</v>
-      </c>
-      <c r="D477" t="s">
-        <v>1037</v>
-      </c>
-      <c r="E477" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="478" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B478" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C478" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D478" t="s">
-        <v>1039</v>
-      </c>
-      <c r="E478" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="479" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B479" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C479" t="s">
-        <v>1041</v>
-      </c>
-      <c r="D479" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E479" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="480" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B480" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C480" t="s">
-        <v>1043</v>
-      </c>
-      <c r="D480" t="s">
-        <v>1043</v>
-      </c>
-      <c r="E480" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="481" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B481" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C481" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D481" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E481" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="482" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B482" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C482" t="s">
-        <v>1047</v>
-      </c>
-      <c r="D482" t="s">
-        <v>1047</v>
-      </c>
-      <c r="E482" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="483" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B483" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C483" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D483" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E483" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="484" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B484" t="s">
-        <v>1050</v>
-      </c>
-      <c r="C484" t="s">
-        <v>1051</v>
-      </c>
-      <c r="D484" t="s">
-        <v>1051</v>
-      </c>
-      <c r="E484" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="485" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B485" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C485" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D485" t="s">
-        <v>1053</v>
-      </c>
-      <c r="E485" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="486" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B486" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C486" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D486" t="s">
-        <v>1055</v>
-      </c>
-      <c r="E486" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="487" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B487" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C487" t="s">
-        <v>1057</v>
-      </c>
-      <c r="D487" t="s">
-        <v>1057</v>
-      </c>
-      <c r="E487" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="488" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B488" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C488" t="s">
-        <v>1059</v>
-      </c>
-      <c r="D488" t="s">
-        <v>1059</v>
-      </c>
-      <c r="E488" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="489" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B489" t="s">
-        <v>1060</v>
-      </c>
-      <c r="C489" t="s">
-        <v>1061</v>
-      </c>
-      <c r="D489" t="s">
-        <v>1061</v>
-      </c>
-      <c r="E489" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="490" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B490" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C490" t="s">
-        <v>1063</v>
-      </c>
-      <c r="D490" t="s">
-        <v>1063</v>
-      </c>
-      <c r="E490" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="491" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B491" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C491" t="s">
-        <v>1065</v>
-      </c>
-      <c r="D491" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E491" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="492" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B492" t="s">
-        <v>1066</v>
-      </c>
-      <c r="C492" t="s">
-        <v>1067</v>
-      </c>
-      <c r="D492" t="s">
-        <v>1067</v>
-      </c>
-      <c r="E492" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="493" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B493" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C493" t="s">
-        <v>1069</v>
-      </c>
-      <c r="D493" t="s">
-        <v>1069</v>
-      </c>
-      <c r="E493" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="494" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B494" t="s">
-        <v>1070</v>
-      </c>
-      <c r="C494" t="s">
-        <v>1071</v>
-      </c>
-      <c r="D494" t="s">
-        <v>1071</v>
-      </c>
-      <c r="E494" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="495" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B495" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C495" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D495" t="s">
-        <v>1073</v>
-      </c>
-      <c r="E495" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="496" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B496" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C496" t="s">
-        <v>1075</v>
-      </c>
-      <c r="D496" t="s">
-        <v>1075</v>
-      </c>
-      <c r="E496" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="497" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B497" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C497" t="s">
-        <v>1077</v>
-      </c>
-      <c r="D497" t="s">
-        <v>1077</v>
-      </c>
-      <c r="E497" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="498" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B498" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C498" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D498" t="s">
-        <v>1079</v>
-      </c>
-      <c r="E498" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="499" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B499" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C499" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D499" t="s">
-        <v>1081</v>
-      </c>
-      <c r="E499" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="500" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B500" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C500" t="s">
-        <v>1083</v>
-      </c>
-      <c r="D500" t="s">
-        <v>1083</v>
-      </c>
-      <c r="E500" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="501" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B501" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C501" t="s">
-        <v>1085</v>
-      </c>
-      <c r="D501" t="s">
-        <v>1085</v>
-      </c>
-      <c r="E501" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="502" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B502" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C502" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D502" t="s">
-        <v>1087</v>
-      </c>
-      <c r="E502" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="503" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B503" t="s">
-        <v>1088</v>
-      </c>
-      <c r="C503" t="s">
-        <v>1089</v>
-      </c>
-      <c r="D503" t="s">
-        <v>1089</v>
-      </c>
-      <c r="E503" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="504" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B504" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C504" t="s">
-        <v>1091</v>
-      </c>
-      <c r="D504" t="s">
-        <v>1091</v>
-      </c>
-      <c r="E504" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="505" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B505" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C505" t="s">
-        <v>1093</v>
-      </c>
-      <c r="D505" t="s">
-        <v>1093</v>
-      </c>
-      <c r="E505" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="506" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B506" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C506" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D506" t="s">
-        <v>1095</v>
-      </c>
-      <c r="E506" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="507" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B507" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C507" t="s">
-        <v>1097</v>
-      </c>
-      <c r="D507" t="s">
-        <v>1097</v>
-      </c>
-      <c r="E507" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="508" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B508" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C508" t="s">
-        <v>1099</v>
-      </c>
-      <c r="D508" t="s">
-        <v>1099</v>
-      </c>
-      <c r="E508" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="509" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B509" t="s">
-        <v>1100</v>
-      </c>
-      <c r="C509" t="s">
-        <v>1101</v>
-      </c>
-      <c r="D509" t="s">
-        <v>1101</v>
-      </c>
-      <c r="E509" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="510" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B510" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C510" t="s">
-        <v>1103</v>
-      </c>
-      <c r="D510" t="s">
-        <v>1103</v>
-      </c>
-      <c r="E510" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="511" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B511" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C511" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D511" t="s">
-        <v>1105</v>
-      </c>
-      <c r="E511" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="512" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B512" t="s">
-        <v>1106</v>
-      </c>
-      <c r="C512" t="s">
-        <v>1107</v>
-      </c>
-      <c r="D512" t="s">
-        <v>1107</v>
-      </c>
-      <c r="E512" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="513" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B513" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C513" t="s">
-        <v>1109</v>
-      </c>
-      <c r="D513" t="s">
-        <v>1109</v>
-      </c>
-      <c r="E513" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="514" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B514" t="s">
-        <v>1110</v>
-      </c>
-      <c r="C514" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D514" t="s">
-        <v>1111</v>
-      </c>
-      <c r="E514" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="515" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B515" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C515" t="s">
-        <v>1113</v>
-      </c>
-      <c r="D515" t="s">
-        <v>1113</v>
-      </c>
-      <c r="E515" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="516" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B516" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C516" t="s">
-        <v>1115</v>
-      </c>
-      <c r="D516" t="s">
-        <v>1115</v>
-      </c>
-      <c r="E516" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="517" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B517" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C517" t="s">
-        <v>1117</v>
-      </c>
-      <c r="D517" t="s">
-        <v>1117</v>
-      </c>
-      <c r="E517" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="518" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B518" t="s">
-        <v>1118</v>
-      </c>
-      <c r="C518" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D518" t="s">
-        <v>1119</v>
-      </c>
-      <c r="E518" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="519" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B519" t="s">
-        <v>1120</v>
-      </c>
-      <c r="C519" t="s">
-        <v>1121</v>
-      </c>
-      <c r="D519" t="s">
-        <v>1121</v>
-      </c>
-      <c r="E519" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="520" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B520" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C520" t="s">
-        <v>1123</v>
-      </c>
-      <c r="D520" t="s">
-        <v>1123</v>
-      </c>
-      <c r="E520" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="521" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B521" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C521" t="s">
-        <v>1125</v>
-      </c>
-      <c r="D521" t="s">
-        <v>1125</v>
-      </c>
-      <c r="E521" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="522" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B522" t="s">
-        <v>1126</v>
-      </c>
-      <c r="C522" t="s">
-        <v>1127</v>
-      </c>
-      <c r="D522" t="s">
-        <v>1127</v>
-      </c>
-      <c r="E522" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="523" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B523" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C523" t="s">
-        <v>1129</v>
-      </c>
-      <c r="D523" t="s">
-        <v>1129</v>
-      </c>
-      <c r="E523" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="524" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B524" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C524" t="s">
-        <v>1131</v>
-      </c>
-      <c r="D524" t="s">
-        <v>1131</v>
-      </c>
-      <c r="E524" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="525" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B525" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C525" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D525" t="s">
-        <v>1133</v>
-      </c>
-      <c r="E525" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="526" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B526" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C526" t="s">
-        <v>1135</v>
-      </c>
-      <c r="D526" t="s">
-        <v>1135</v>
-      </c>
-      <c r="E526" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="527" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B527" t="s">
-        <v>1136</v>
-      </c>
-      <c r="C527" t="s">
-        <v>1137</v>
-      </c>
-      <c r="D527" t="s">
-        <v>1137</v>
-      </c>
-      <c r="E527" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="528" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B528" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C528" t="s">
-        <v>1139</v>
-      </c>
-      <c r="D528" t="s">
-        <v>1139</v>
-      </c>
-      <c r="E528" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="529" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B529" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C529" t="s">
-        <v>1141</v>
-      </c>
-      <c r="D529" t="s">
-        <v>1141</v>
-      </c>
-      <c r="E529" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="530" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B530" t="s">
-        <v>1142</v>
-      </c>
-      <c r="C530" t="s">
-        <v>1143</v>
-      </c>
-      <c r="D530" t="s">
-        <v>1143</v>
-      </c>
-      <c r="E530" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="531" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B531" t="s">
-        <v>1144</v>
-      </c>
-      <c r="C531" t="s">
-        <v>1145</v>
-      </c>
-      <c r="D531" t="s">
-        <v>1145</v>
-      </c>
-      <c r="E531" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="532" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B532" t="s">
-        <v>1146</v>
-      </c>
-      <c r="C532" t="s">
-        <v>1147</v>
-      </c>
-      <c r="D532" t="s">
-        <v>1147</v>
-      </c>
-      <c r="E532" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="533" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B533" t="s">
-        <v>1148</v>
-      </c>
-      <c r="C533" t="s">
-        <v>1149</v>
-      </c>
-      <c r="D533" t="s">
-        <v>1149</v>
-      </c>
-      <c r="E533" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="534" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B534" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C534" t="s">
-        <v>1151</v>
-      </c>
-      <c r="D534" t="s">
-        <v>1151</v>
-      </c>
-      <c r="E534" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="535" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B535" t="s">
-        <v>1152</v>
-      </c>
-      <c r="C535" t="s">
-        <v>1153</v>
-      </c>
-      <c r="D535" t="s">
-        <v>1153</v>
-      </c>
-      <c r="E535" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="536" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B536" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C536" t="s">
-        <v>1155</v>
-      </c>
-      <c r="D536" t="s">
-        <v>1155</v>
-      </c>
-      <c r="E536" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="537" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B537" t="s">
-        <v>1156</v>
-      </c>
-      <c r="C537" t="s">
-        <v>1157</v>
-      </c>
-      <c r="D537" t="s">
-        <v>1157</v>
-      </c>
-      <c r="E537" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="538" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B538" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C538" t="s">
-        <v>1159</v>
-      </c>
-      <c r="D538" t="s">
-        <v>1159</v>
-      </c>
-      <c r="E538" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="539" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B539" t="s">
-        <v>1160</v>
-      </c>
-      <c r="C539" t="s">
-        <v>1161</v>
-      </c>
-      <c r="D539" t="s">
-        <v>1161</v>
-      </c>
-      <c r="E539" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="540" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B540" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C540" t="s">
-        <v>1163</v>
-      </c>
-      <c r="D540" t="s">
-        <v>1163</v>
-      </c>
-      <c r="E540" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="541" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B541" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C541" t="s">
-        <v>1165</v>
-      </c>
-      <c r="D541" t="s">
-        <v>1165</v>
-      </c>
-      <c r="E541" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="542" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B542" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C542" t="s">
-        <v>1167</v>
-      </c>
-      <c r="D542" t="s">
-        <v>1167</v>
-      </c>
-      <c r="E542" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="543" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B543" t="s">
-        <v>1168</v>
-      </c>
-      <c r="C543" t="s">
-        <v>1169</v>
-      </c>
-      <c r="D543" t="s">
-        <v>1169</v>
-      </c>
-      <c r="E543" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="544" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B544" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C544" t="s">
-        <v>1171</v>
-      </c>
-      <c r="D544" t="s">
-        <v>1171</v>
-      </c>
-      <c r="E544" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="545" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B545" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C545" t="s">
-        <v>1173</v>
-      </c>
-      <c r="D545" t="s">
-        <v>1173</v>
-      </c>
-      <c r="E545" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="546" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B546" t="s">
-        <v>1174</v>
-      </c>
-      <c r="C546" t="s">
-        <v>1175</v>
-      </c>
-      <c r="D546" t="s">
-        <v>1175</v>
-      </c>
-      <c r="E546" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="547" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B547" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C547" t="s">
-        <v>1177</v>
-      </c>
-      <c r="D547" t="s">
-        <v>1177</v>
-      </c>
-      <c r="E547" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="548" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B548" t="s">
-        <v>1178</v>
-      </c>
-      <c r="C548" t="s">
-        <v>1179</v>
-      </c>
-      <c r="D548" t="s">
-        <v>1179</v>
-      </c>
-      <c r="E548" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="549" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B549" t="s">
-        <v>1180</v>
-      </c>
-      <c r="C549" t="s">
-        <v>1181</v>
-      </c>
-      <c r="D549" t="s">
-        <v>1181</v>
-      </c>
-      <c r="E549" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="550" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B550" t="s">
-        <v>1182</v>
-      </c>
-      <c r="C550" t="s">
-        <v>1183</v>
-      </c>
-      <c r="D550" t="s">
-        <v>1183</v>
-      </c>
-      <c r="E550" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="551" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B551" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C551" t="s">
-        <v>1185</v>
-      </c>
-      <c r="D551" t="s">
-        <v>1185</v>
-      </c>
-      <c r="E551" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="552" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B552" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C552" t="s">
-        <v>1187</v>
-      </c>
-      <c r="D552" t="s">
-        <v>1187</v>
-      </c>
-      <c r="E552" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="553" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B553" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C553" t="s">
-        <v>1189</v>
-      </c>
-      <c r="D553" t="s">
-        <v>1189</v>
-      </c>
-      <c r="E553" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="554" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B554" t="s">
-        <v>1190</v>
-      </c>
-      <c r="C554" t="s">
-        <v>1191</v>
-      </c>
-      <c r="D554" t="s">
-        <v>1191</v>
-      </c>
-      <c r="E554" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="555" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B555" t="s">
-        <v>1192</v>
-      </c>
-      <c r="C555" t="s">
-        <v>1193</v>
-      </c>
-      <c r="D555" t="s">
-        <v>1193</v>
-      </c>
-      <c r="E555" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="556" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B556" t="s">
-        <v>1194</v>
-      </c>
-      <c r="C556" t="s">
-        <v>1195</v>
-      </c>
-      <c r="D556" t="s">
-        <v>1195</v>
-      </c>
-      <c r="E556" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="557" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B557" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C557" t="s">
-        <v>1197</v>
-      </c>
-      <c r="D557" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E557" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="558" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B558" t="s">
-        <v>1198</v>
-      </c>
-      <c r="C558" t="s">
-        <v>1199</v>
-      </c>
-      <c r="D558" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E558" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="559" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B559" t="s">
-        <v>1200</v>
-      </c>
-      <c r="C559" t="s">
-        <v>1201</v>
-      </c>
-      <c r="D559" t="s">
-        <v>1201</v>
-      </c>
-      <c r="E559" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="560" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B560" t="s">
-        <v>1202</v>
-      </c>
-      <c r="C560" t="s">
-        <v>1203</v>
-      </c>
-      <c r="D560" t="s">
-        <v>1203</v>
-      </c>
-      <c r="E560" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="561" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B561" t="s">
-        <v>1204</v>
-      </c>
-      <c r="C561" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D561" t="s">
-        <v>1205</v>
-      </c>
-      <c r="E561" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="562" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B562" t="s">
-        <v>1206</v>
-      </c>
-      <c r="C562" t="s">
-        <v>1207</v>
-      </c>
-      <c r="D562" t="s">
-        <v>1207</v>
-      </c>
-      <c r="E562" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="563" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B563" t="s">
-        <v>1208</v>
-      </c>
-      <c r="C563" t="s">
-        <v>1209</v>
-      </c>
-      <c r="D563" t="s">
-        <v>1209</v>
-      </c>
-      <c r="E563" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="564" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B564" t="s">
-        <v>1210</v>
-      </c>
-      <c r="C564" t="s">
-        <v>1211</v>
-      </c>
-      <c r="D564" t="s">
-        <v>1211</v>
-      </c>
-      <c r="E564" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="565" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B565" t="s">
-        <v>1212</v>
-      </c>
-      <c r="C565" t="s">
-        <v>1213</v>
-      </c>
-      <c r="D565" t="s">
-        <v>1213</v>
-      </c>
-      <c r="E565" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="566" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B566" t="s">
-        <v>1214</v>
-      </c>
-      <c r="C566" t="s">
-        <v>1215</v>
-      </c>
-      <c r="D566" t="s">
-        <v>1215</v>
-      </c>
-      <c r="E566" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="567" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B567" t="s">
-        <v>1216</v>
-      </c>
-      <c r="C567" t="s">
-        <v>1217</v>
-      </c>
-      <c r="D567" t="s">
-        <v>1217</v>
-      </c>
-      <c r="E567" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="568" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B568" t="s">
-        <v>1218</v>
-      </c>
-      <c r="C568" t="s">
-        <v>1219</v>
-      </c>
-      <c r="D568" t="s">
-        <v>1219</v>
-      </c>
-      <c r="E568" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="569" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B569" t="s">
-        <v>1220</v>
-      </c>
-      <c r="C569" t="s">
-        <v>1221</v>
-      </c>
-      <c r="D569" t="s">
-        <v>1221</v>
-      </c>
-      <c r="E569" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="570" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B570" t="s">
-        <v>1222</v>
-      </c>
-      <c r="C570" t="s">
-        <v>1223</v>
-      </c>
-      <c r="D570" t="s">
-        <v>1223</v>
-      </c>
-      <c r="E570" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="571" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B571" t="s">
-        <v>1224</v>
-      </c>
-      <c r="C571" t="s">
-        <v>1225</v>
-      </c>
-      <c r="D571" t="s">
-        <v>1225</v>
-      </c>
-      <c r="E571" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="572" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B572" t="s">
-        <v>1226</v>
-      </c>
-      <c r="C572" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D572" t="s">
-        <v>1227</v>
-      </c>
-      <c r="E572" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="573" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B573" t="s">
-        <v>1228</v>
-      </c>
-      <c r="C573" t="s">
-        <v>1229</v>
-      </c>
-      <c r="D573" t="s">
-        <v>1229</v>
-      </c>
-      <c r="E573" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="574" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B574" t="s">
-        <v>1230</v>
-      </c>
-      <c r="C574" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D574" t="s">
-        <v>1231</v>
-      </c>
-      <c r="E574" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="575" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B575" t="s">
-        <v>1232</v>
-      </c>
-      <c r="C575" t="s">
-        <v>1233</v>
-      </c>
-      <c r="D575" t="s">
-        <v>1233</v>
-      </c>
-      <c r="E575" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="576" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B576" t="s">
-        <v>1234</v>
-      </c>
-      <c r="C576" t="s">
-        <v>1235</v>
-      </c>
-      <c r="D576" t="s">
-        <v>1235</v>
-      </c>
-      <c r="E576" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="577" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B577" t="s">
-        <v>1236</v>
-      </c>
-      <c r="C577" t="s">
-        <v>1237</v>
-      </c>
-      <c r="D577" t="s">
-        <v>1237</v>
-      </c>
-      <c r="E577" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="578" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B578" t="s">
-        <v>1238</v>
-      </c>
-      <c r="C578" t="s">
-        <v>1239</v>
-      </c>
-      <c r="D578" t="s">
-        <v>1239</v>
-      </c>
-      <c r="E578" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="579" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B579" t="s">
-        <v>1240</v>
-      </c>
-      <c r="C579" t="s">
-        <v>1241</v>
-      </c>
-      <c r="D579" t="s">
-        <v>1241</v>
-      </c>
-      <c r="E579" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="580" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B580" t="s">
-        <v>1242</v>
-      </c>
-      <c r="C580" t="s">
-        <v>1243</v>
-      </c>
-      <c r="D580" t="s">
-        <v>1243</v>
-      </c>
-      <c r="E580" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="581" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B581" t="s">
-        <v>1244</v>
-      </c>
-      <c r="C581" t="s">
-        <v>1245</v>
-      </c>
-      <c r="D581" t="s">
-        <v>1245</v>
-      </c>
-      <c r="E581" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="582" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B582" t="s">
-        <v>1246</v>
-      </c>
-      <c r="C582" t="s">
-        <v>1247</v>
-      </c>
-      <c r="D582" t="s">
-        <v>1247</v>
-      </c>
-      <c r="E582" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="583" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B583" t="s">
-        <v>1248</v>
-      </c>
-      <c r="C583" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D583" t="s">
-        <v>1249</v>
-      </c>
-      <c r="E583" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="584" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B584" t="s">
-        <v>1250</v>
-      </c>
-      <c r="C584" t="s">
-        <v>1251</v>
-      </c>
-      <c r="D584" t="s">
-        <v>1251</v>
-      </c>
-      <c r="E584" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="585" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B585" t="s">
-        <v>1252</v>
-      </c>
-      <c r="C585" t="s">
-        <v>1253</v>
-      </c>
-      <c r="D585" t="s">
-        <v>1253</v>
-      </c>
-      <c r="E585" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="586" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B586" t="s">
-        <v>1254</v>
-      </c>
-      <c r="C586" t="s">
-        <v>1255</v>
-      </c>
-      <c r="D586" t="s">
-        <v>1255</v>
-      </c>
-      <c r="E586" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="587" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B587" t="s">
-        <v>1256</v>
-      </c>
-      <c r="C587" t="s">
-        <v>1257</v>
-      </c>
-      <c r="D587" t="s">
-        <v>1257</v>
-      </c>
-      <c r="E587" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="588" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B588" t="s">
-        <v>1258</v>
-      </c>
-      <c r="C588" t="s">
-        <v>1259</v>
-      </c>
-      <c r="D588" t="s">
-        <v>1259</v>
-      </c>
-      <c r="E588" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="589" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B589" t="s">
-        <v>1260</v>
-      </c>
-      <c r="C589" t="s">
-        <v>1261</v>
-      </c>
-      <c r="D589" t="s">
-        <v>1261</v>
-      </c>
-      <c r="E589" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="590" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B590" t="s">
-        <v>1262</v>
-      </c>
-      <c r="C590" t="s">
-        <v>1263</v>
-      </c>
-      <c r="D590" t="s">
-        <v>1263</v>
-      </c>
-      <c r="E590" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="591" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B591" t="s">
-        <v>1264</v>
-      </c>
-      <c r="C591" t="s">
-        <v>1265</v>
-      </c>
-      <c r="D591" t="s">
-        <v>1265</v>
-      </c>
-      <c r="E591" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="592" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B592" t="s">
-        <v>1266</v>
-      </c>
-      <c r="C592" t="s">
-        <v>1267</v>
-      </c>
-      <c r="D592" t="s">
-        <v>1267</v>
-      </c>
-      <c r="E592" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="593" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B593" t="s">
-        <v>1268</v>
-      </c>
-      <c r="C593" t="s">
-        <v>1269</v>
-      </c>
-      <c r="D593" t="s">
-        <v>1269</v>
-      </c>
-      <c r="E593" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="594" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B594" t="s">
-        <v>1270</v>
-      </c>
-      <c r="C594" t="s">
-        <v>1271</v>
-      </c>
-      <c r="D594" t="s">
-        <v>1271</v>
-      </c>
-      <c r="E594" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="595" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B595" t="s">
-        <v>1272</v>
-      </c>
-      <c r="C595" t="s">
-        <v>1273</v>
-      </c>
-      <c r="D595" t="s">
-        <v>1273</v>
-      </c>
-      <c r="E595" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="596" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B596" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C596" t="s">
-        <v>1275</v>
-      </c>
-      <c r="D596" t="s">
-        <v>1275</v>
-      </c>
-      <c r="E596" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="597" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B597" t="s">
-        <v>1276</v>
-      </c>
-      <c r="C597" t="s">
-        <v>1277</v>
-      </c>
-      <c r="D597" t="s">
-        <v>1277</v>
-      </c>
-      <c r="E597" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="598" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B598" t="s">
-        <v>1278</v>
-      </c>
-      <c r="C598" t="s">
-        <v>1279</v>
-      </c>
-      <c r="D598" t="s">
-        <v>1279</v>
-      </c>
-      <c r="E598" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="599" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B599" t="s">
-        <v>1280</v>
-      </c>
-      <c r="C599" t="s">
-        <v>1281</v>
-      </c>
-      <c r="D599" t="s">
-        <v>1281</v>
-      </c>
-      <c r="E599" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="600" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B600" t="s">
-        <v>1282</v>
-      </c>
-      <c r="C600" t="s">
-        <v>1283</v>
-      </c>
-      <c r="D600" t="s">
-        <v>1283</v>
-      </c>
-      <c r="E600" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="601" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B601" t="s">
-        <v>1284</v>
-      </c>
-      <c r="C601" t="s">
-        <v>1285</v>
-      </c>
-      <c r="D601" t="s">
-        <v>1285</v>
-      </c>
-      <c r="E601" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="602" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B602" t="s">
-        <v>1286</v>
-      </c>
-      <c r="C602" t="s">
-        <v>1287</v>
-      </c>
-      <c r="D602" t="s">
-        <v>1287</v>
-      </c>
-      <c r="E602" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="603" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B603" t="s">
-        <v>1288</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1289</v>
-      </c>
-      <c r="D603" t="s">
-        <v>1289</v>
-      </c>
-      <c r="E603" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="604" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B604" t="s">
-        <v>1290</v>
-      </c>
-      <c r="C604" t="s">
-        <v>1291</v>
-      </c>
-      <c r="D604" t="s">
-        <v>1291</v>
-      </c>
-      <c r="E604" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="605" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B605" t="s">
-        <v>1292</v>
-      </c>
-      <c r="C605" t="s">
-        <v>1293</v>
-      </c>
-      <c r="D605" t="s">
-        <v>1293</v>
-      </c>
-      <c r="E605" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="606" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B606" t="s">
-        <v>1294</v>
-      </c>
-      <c r="C606" t="s">
-        <v>1295</v>
-      </c>
-      <c r="D606" t="s">
-        <v>1295</v>
-      </c>
-      <c r="E606" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="607" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B607" t="s">
-        <v>1296</v>
-      </c>
-      <c r="C607" t="s">
-        <v>1297</v>
-      </c>
-      <c r="D607" t="s">
-        <v>1297</v>
-      </c>
-      <c r="E607" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="608" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B608" t="s">
-        <v>1298</v>
-      </c>
-      <c r="C608" t="s">
-        <v>1299</v>
-      </c>
-      <c r="D608" t="s">
-        <v>1299</v>
-      </c>
-      <c r="E608" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="609" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B609" t="s">
-        <v>1300</v>
-      </c>
-      <c r="C609" t="s">
-        <v>1301</v>
-      </c>
-      <c r="D609" t="s">
-        <v>1301</v>
-      </c>
-      <c r="E609" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="610" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B610" t="s">
-        <v>1302</v>
-      </c>
-      <c r="C610" t="s">
-        <v>1303</v>
-      </c>
-      <c r="D610" t="s">
-        <v>1303</v>
-      </c>
-      <c r="E610" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="611" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B611" t="s">
-        <v>1304</v>
-      </c>
-      <c r="C611" t="s">
-        <v>1305</v>
-      </c>
-      <c r="D611" t="s">
-        <v>1305</v>
-      </c>
-      <c r="E611" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="612" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B612" t="s">
-        <v>1306</v>
-      </c>
-      <c r="C612" t="s">
-        <v>1307</v>
-      </c>
-      <c r="D612" t="s">
-        <v>1307</v>
-      </c>
-      <c r="E612" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="613" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B613" t="s">
-        <v>1308</v>
-      </c>
-      <c r="C613" t="s">
-        <v>1309</v>
-      </c>
-      <c r="D613" t="s">
-        <v>1309</v>
-      </c>
-      <c r="E613" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="614" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B614" t="s">
-        <v>1310</v>
-      </c>
-      <c r="C614" t="s">
-        <v>1311</v>
-      </c>
-      <c r="D614" t="s">
-        <v>1311</v>
-      </c>
-      <c r="E614" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="615" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B615" t="s">
-        <v>1312</v>
-      </c>
-      <c r="C615" t="s">
-        <v>1313</v>
-      </c>
-      <c r="D615" t="s">
-        <v>1313</v>
-      </c>
-      <c r="E615" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="616" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B616" t="s">
-        <v>1314</v>
-      </c>
-      <c r="C616" t="s">
-        <v>1315</v>
-      </c>
-      <c r="D616" t="s">
-        <v>1315</v>
-      </c>
-      <c r="E616" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="617" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B617" t="s">
-        <v>1316</v>
-      </c>
-      <c r="C617" t="s">
-        <v>1317</v>
-      </c>
-      <c r="D617" t="s">
-        <v>1317</v>
-      </c>
-      <c r="E617" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="618" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B618" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C618" t="s">
-        <v>1319</v>
-      </c>
-      <c r="D618" t="s">
-        <v>1319</v>
-      </c>
-      <c r="E618" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="619" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B619" t="s">
-        <v>1320</v>
-      </c>
-      <c r="C619" t="s">
-        <v>1321</v>
-      </c>
-      <c r="D619" t="s">
-        <v>1321</v>
-      </c>
-      <c r="E619" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="620" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B620" t="s">
-        <v>1322</v>
-      </c>
-      <c r="C620" t="s">
-        <v>1323</v>
-      </c>
-      <c r="D620" t="s">
-        <v>1323</v>
-      </c>
-      <c r="E620" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="621" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B621" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C621" t="s">
-        <v>1325</v>
-      </c>
-      <c r="D621" t="s">
-        <v>1325</v>
-      </c>
-      <c r="E621" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="622" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B622" t="s">
-        <v>1326</v>
-      </c>
-      <c r="C622" t="s">
-        <v>1327</v>
-      </c>
-      <c r="D622" t="s">
-        <v>1327</v>
-      </c>
-      <c r="E622" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="623" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B623" t="s">
-        <v>1328</v>
-      </c>
-      <c r="C623" t="s">
-        <v>1329</v>
-      </c>
-      <c r="D623" t="s">
-        <v>1329</v>
-      </c>
-      <c r="E623" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="624" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B624" t="s">
-        <v>1330</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1331</v>
-      </c>
-      <c r="D624" t="s">
-        <v>1331</v>
-      </c>
-      <c r="E624" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="625" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B625" t="s">
-        <v>1332</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1333</v>
-      </c>
-      <c r="D625" t="s">
-        <v>1333</v>
-      </c>
-      <c r="E625" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="626" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B626" t="s">
-        <v>1334</v>
-      </c>
-      <c r="C626" t="s">
-        <v>1335</v>
-      </c>
-      <c r="D626" t="s">
-        <v>1335</v>
-      </c>
-      <c r="E626" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="627" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B627" t="s">
-        <v>1336</v>
-      </c>
-      <c r="C627" t="s">
-        <v>1337</v>
-      </c>
-      <c r="D627" t="s">
-        <v>1337</v>
-      </c>
-      <c r="E627" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="628" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B628" t="s">
-        <v>1338</v>
-      </c>
-      <c r="C628" t="s">
-        <v>1339</v>
-      </c>
-      <c r="D628" t="s">
-        <v>1339</v>
-      </c>
-      <c r="E628" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="629" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B629" t="s">
-        <v>1340</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1341</v>
-      </c>
-      <c r="D629" t="s">
-        <v>1341</v>
-      </c>
-      <c r="E629" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="630" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B630" t="s">
-        <v>1342</v>
-      </c>
-      <c r="C630" t="s">
-        <v>1343</v>
-      </c>
-      <c r="D630" t="s">
-        <v>1343</v>
-      </c>
-      <c r="E630" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="631" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B631" t="s">
-        <v>1344</v>
-      </c>
-      <c r="C631" t="s">
-        <v>1345</v>
-      </c>
-      <c r="D631" t="s">
-        <v>1345</v>
-      </c>
-      <c r="E631" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="632" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B632" t="s">
-        <v>1346</v>
-      </c>
-      <c r="C632" t="s">
-        <v>1347</v>
-      </c>
-      <c r="D632" t="s">
-        <v>1347</v>
-      </c>
-      <c r="E632" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="633" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B633" t="s">
-        <v>1348</v>
-      </c>
-      <c r="C633" t="s">
-        <v>1349</v>
-      </c>
-      <c r="D633" t="s">
-        <v>1349</v>
-      </c>
-      <c r="E633" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="634" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B634" t="s">
-        <v>1350</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1351</v>
-      </c>
-      <c r="D634" t="s">
-        <v>1351</v>
-      </c>
-      <c r="E634" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="635" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B635" t="s">
-        <v>1352</v>
-      </c>
-      <c r="C635" t="s">
-        <v>1353</v>
-      </c>
-      <c r="D635" t="s">
-        <v>1353</v>
-      </c>
-      <c r="E635" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="636" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B636" t="s">
-        <v>1354</v>
-      </c>
-      <c r="C636" t="s">
-        <v>1355</v>
-      </c>
-      <c r="D636" t="s">
-        <v>1355</v>
-      </c>
-      <c r="E636" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="637" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B637" t="s">
-        <v>1356</v>
-      </c>
-      <c r="C637" t="s">
-        <v>1357</v>
-      </c>
-      <c r="D637" t="s">
-        <v>1357</v>
-      </c>
-      <c r="E637" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="638" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B638" t="s">
-        <v>1358</v>
-      </c>
-      <c r="C638" t="s">
-        <v>1359</v>
-      </c>
-      <c r="D638" t="s">
-        <v>1359</v>
-      </c>
-      <c r="E638" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="639" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B639" t="s">
-        <v>1360</v>
-      </c>
-      <c r="C639" t="s">
-        <v>1361</v>
-      </c>
-      <c r="D639" t="s">
-        <v>1361</v>
-      </c>
-      <c r="E639" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="640" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B640" t="s">
-        <v>1362</v>
-      </c>
-      <c r="C640" t="s">
-        <v>1363</v>
-      </c>
-      <c r="D640" t="s">
-        <v>1363</v>
-      </c>
-      <c r="E640" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="641" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B641" t="s">
-        <v>1364</v>
-      </c>
-      <c r="C641" t="s">
-        <v>1365</v>
-      </c>
-      <c r="D641" t="s">
-        <v>1365</v>
-      </c>
-      <c r="E641" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="642" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B642" t="s">
-        <v>1366</v>
-      </c>
-      <c r="C642" t="s">
-        <v>1367</v>
-      </c>
-      <c r="D642" t="s">
-        <v>1367</v>
-      </c>
-      <c r="E642" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="643" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B643" t="s">
-        <v>1368</v>
-      </c>
-      <c r="C643" t="s">
-        <v>1369</v>
-      </c>
-      <c r="D643" t="s">
-        <v>1369</v>
-      </c>
-      <c r="E643" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="644" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B644" t="s">
-        <v>1370</v>
-      </c>
-      <c r="C644" t="s">
-        <v>1371</v>
-      </c>
-      <c r="D644" t="s">
-        <v>1371</v>
-      </c>
-      <c r="E644" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="645" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B645" t="s">
-        <v>1372</v>
-      </c>
-      <c r="C645" t="s">
-        <v>1373</v>
-      </c>
-      <c r="D645" t="s">
-        <v>1373</v>
-      </c>
-      <c r="E645" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="646" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B646" t="s">
-        <v>1374</v>
-      </c>
-      <c r="C646" t="s">
-        <v>1375</v>
-      </c>
-      <c r="D646" t="s">
-        <v>1375</v>
-      </c>
-      <c r="E646" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="647" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B647" t="s">
-        <v>1376</v>
-      </c>
-      <c r="C647" t="s">
-        <v>1377</v>
-      </c>
-      <c r="D647" t="s">
-        <v>1377</v>
-      </c>
-      <c r="E647" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="648" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B648" t="s">
-        <v>1378</v>
-      </c>
-      <c r="C648" t="s">
-        <v>1379</v>
-      </c>
-      <c r="D648" t="s">
-        <v>1379</v>
-      </c>
-      <c r="E648" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="649" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B649" t="s">
-        <v>1380</v>
-      </c>
-      <c r="C649" t="s">
-        <v>1381</v>
-      </c>
-      <c r="D649" t="s">
-        <v>1381</v>
-      </c>
-      <c r="E649" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="650" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B650" t="s">
-        <v>1382</v>
-      </c>
-      <c r="C650" t="s">
-        <v>1383</v>
-      </c>
-      <c r="D650" t="s">
-        <v>1383</v>
-      </c>
-      <c r="E650" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="651" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B651" t="s">
-        <v>1384</v>
-      </c>
-      <c r="C651" t="s">
-        <v>1385</v>
-      </c>
-      <c r="D651" t="s">
-        <v>1385</v>
-      </c>
-      <c r="E651" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="652" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B652" t="s">
-        <v>1386</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1387</v>
-      </c>
-      <c r="D652" t="s">
-        <v>1387</v>
-      </c>
-      <c r="E652" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="653" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B653" t="s">
-        <v>1388</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1389</v>
-      </c>
-      <c r="D653" t="s">
-        <v>1389</v>
-      </c>
-      <c r="E653" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="654" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B654" t="s">
-        <v>1390</v>
-      </c>
-      <c r="C654" t="s">
-        <v>1391</v>
-      </c>
-      <c r="D654" t="s">
-        <v>1391</v>
-      </c>
-      <c r="E654" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="655" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B655" t="s">
-        <v>1392</v>
-      </c>
-      <c r="C655" t="s">
-        <v>1393</v>
-      </c>
-      <c r="D655" t="s">
-        <v>1393</v>
-      </c>
-      <c r="E655" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="656" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B656" t="s">
-        <v>1394</v>
-      </c>
-      <c r="C656" t="s">
-        <v>1395</v>
-      </c>
-      <c r="D656" t="s">
-        <v>1395</v>
-      </c>
-      <c r="E656" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="657" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B657" t="s">
-        <v>1396</v>
-      </c>
-      <c r="C657" t="s">
-        <v>1397</v>
-      </c>
-      <c r="D657" t="s">
-        <v>1397</v>
-      </c>
-      <c r="E657" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="658" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B658" t="s">
-        <v>1398</v>
-      </c>
-      <c r="C658" t="s">
-        <v>1399</v>
-      </c>
-      <c r="D658" t="s">
-        <v>1399</v>
-      </c>
-      <c r="E658" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="659" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B659" t="s">
-        <v>1400</v>
-      </c>
-      <c r="C659" t="s">
-        <v>1401</v>
-      </c>
-      <c r="D659" t="s">
-        <v>1401</v>
-      </c>
-      <c r="E659" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="660" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B660" t="s">
-        <v>1402</v>
-      </c>
-      <c r="C660" t="s">
-        <v>1403</v>
-      </c>
-      <c r="D660" t="s">
-        <v>1403</v>
-      </c>
-      <c r="E660" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="661" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B661" t="s">
-        <v>1404</v>
-      </c>
-      <c r="C661" t="s">
-        <v>1405</v>
-      </c>
-      <c r="D661" t="s">
-        <v>1405</v>
-      </c>
-      <c r="E661" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="662" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B662" t="s">
-        <v>1406</v>
-      </c>
-      <c r="C662" t="s">
-        <v>1407</v>
-      </c>
-      <c r="D662" t="s">
-        <v>1407</v>
-      </c>
-      <c r="E662" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="663" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B663" t="s">
-        <v>1408</v>
-      </c>
-      <c r="C663" t="s">
-        <v>1409</v>
-      </c>
-      <c r="D663" t="s">
-        <v>1409</v>
-      </c>
-      <c r="E663" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="664" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B664" t="s">
-        <v>1410</v>
-      </c>
-      <c r="C664" t="s">
-        <v>1411</v>
-      </c>
-      <c r="D664" t="s">
-        <v>1411</v>
-      </c>
-      <c r="E664" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="665" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B665" t="s">
-        <v>1412</v>
-      </c>
-      <c r="C665" t="s">
-        <v>1413</v>
-      </c>
-      <c r="D665" t="s">
-        <v>1413</v>
-      </c>
-      <c r="E665" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="666" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B666" t="s">
-        <v>1414</v>
-      </c>
-      <c r="C666" t="s">
-        <v>1415</v>
-      </c>
-      <c r="D666" t="s">
-        <v>1415</v>
-      </c>
-      <c r="E666" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="667" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B667" t="s">
-        <v>1416</v>
-      </c>
-      <c r="C667" t="s">
-        <v>1417</v>
-      </c>
-      <c r="D667" t="s">
-        <v>1417</v>
-      </c>
-      <c r="E667" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="668" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B668" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C668" t="s">
-        <v>1419</v>
-      </c>
-      <c r="D668" t="s">
-        <v>1419</v>
-      </c>
-      <c r="E668" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="669" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B669" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C669" t="s">
-        <v>1421</v>
-      </c>
-      <c r="D669" t="s">
-        <v>1421</v>
-      </c>
-      <c r="E669" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="670" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B670" t="s">
-        <v>1422</v>
-      </c>
-      <c r="C670" t="s">
-        <v>1423</v>
-      </c>
-      <c r="D670" t="s">
-        <v>1423</v>
-      </c>
-      <c r="E670" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="671" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B671" t="s">
-        <v>1424</v>
-      </c>
-      <c r="C671" t="s">
-        <v>1425</v>
-      </c>
-      <c r="D671" t="s">
-        <v>1425</v>
-      </c>
-      <c r="E671" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="672" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B672" t="s">
-        <v>1426</v>
-      </c>
-      <c r="C672" t="s">
-        <v>1427</v>
-      </c>
-      <c r="D672" t="s">
-        <v>1427</v>
-      </c>
-      <c r="E672" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="673" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B673" t="s">
-        <v>1428</v>
-      </c>
-      <c r="C673" t="s">
-        <v>1429</v>
-      </c>
-      <c r="D673" t="s">
-        <v>1429</v>
-      </c>
-      <c r="E673" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="674" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B674" t="s">
-        <v>1430</v>
-      </c>
-      <c r="C674" t="s">
-        <v>1431</v>
-      </c>
-      <c r="D674" t="s">
-        <v>1431</v>
-      </c>
-      <c r="E674" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="675" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B675" t="s">
-        <v>1432</v>
-      </c>
-      <c r="C675" t="s">
-        <v>1433</v>
-      </c>
-      <c r="D675" t="s">
-        <v>1433</v>
-      </c>
-      <c r="E675" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="676" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B676" t="s">
-        <v>1434</v>
-      </c>
-      <c r="C676" t="s">
-        <v>1435</v>
-      </c>
-      <c r="D676" t="s">
-        <v>1435</v>
-      </c>
-      <c r="E676" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="677" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B677" t="s">
-        <v>1436</v>
-      </c>
-      <c r="C677" t="s">
-        <v>1437</v>
-      </c>
-      <c r="D677" t="s">
-        <v>1437</v>
-      </c>
-      <c r="E677" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="678" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B678" t="s">
-        <v>1438</v>
-      </c>
-      <c r="C678" t="s">
-        <v>1439</v>
-      </c>
-      <c r="D678" t="s">
-        <v>1439</v>
-      </c>
-      <c r="E678" t="s">
         <v>105</v>
       </c>
     </row>
